--- a/BANCO_PREGUNTAS_GENERALES.xlsx
+++ b/BANCO_PREGUNTAS_GENERALES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,6 +505,1466 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PAT_00001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Caída de cabello (Alopecia)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sintoma_Causa_Patologia</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Seleccione las DOS afirmaciones que se relacionan correctamente con Caída de cabello (Alopecia).</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Puede estar asociada principalmente a Espolón calcáneo / dolor de talón (fascitis plantar asociada)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Puede estar asociada a Androgenética (DHT)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Se relaciona principalmente con Insomnio</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Se relaciona con Disminución de densidad</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:59:11</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PAT_00002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Salud prostática / Molestias prostáticas</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sintoma_Causa_Patologia</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Seleccione las DOS afirmaciones que se relacionan correctamente con Salud prostática / Molestias prostáticas.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Se relaciona con Chorro débil</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Puede estar asociada principalmente a Dolor muscular, contracturas y molestias musculoesqueléticas localizadas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Puede estar asociada a Hiperplasia prostática benigna</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Se relaciona principalmente con Quistes ováricos funcionales</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:59:11</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PAT_00003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Disfunción sexual masculina / Dificultad para la erección</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sintoma_Causa_Patologia</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Seleccione las DOS afirmaciones que se relacionan correctamente con Disfunción sexual masculina / Dificultad para la erección.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Puede estar asociada a Estrés o ansiedad</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Se relaciona principalmente con Perimenopausia / Menopausia</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Puede estar asociada principalmente a Endometriosis</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Se relaciona con Disminución de la libido</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:59:11</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>P003</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PAT_00004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Vitalidad masculina y apoyo hormonal (Hipogonadismo / Deficiencia de testosterona*)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sintoma_Causa_Patologia</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Seleccione las DOS afirmaciones que se relacionan correctamente con Vitalidad masculina y apoyo hormonal (Hipogonadismo / Deficiencia de testosterona*).</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Puede estar asociada principalmente a Ciática / Lumbalgia</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Se relaciona con Disminución de la libido</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Puede estar asociada a Envejecimiento</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Se relaciona principalmente con Insomnio</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:59:11</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PAT_00005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Control glucémico (Diabetes mellitus tipo 2 / Prediabetes)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sintoma_Causa_Patologia</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Seleccione las DOS afirmaciones que se relacionan correctamente con Control glucémico (Diabetes mellitus tipo 2 / Prediabetes).</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Se relaciona con Diagnóstico de diabetes o prediabetes</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Puede estar asociada a Resistencia a la insulina</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Puede estar asociada principalmente a Artritis inflamatoria</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Se relaciona principalmente con Quistes ováricos funcionales</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:59:11</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PAT_00006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Perimenopausia / Menopausia</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sintoma_Causa_Patologia</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Seleccione las DOS afirmaciones que se relacionan correctamente con Perimenopausia / Menopausia.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Se relaciona con Alteraciones menstruales</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Puede estar asociada a Disminución fisiológica de estrógenos y progesterona</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Puede estar asociada principalmente a Espolón calcáneo / dolor de talón (fascitis plantar asociada)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Se relaciona principalmente con Insomnio</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:59:11</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PAT_00007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Insomnio</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sintoma_Causa_Patologia</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Seleccione las DOS afirmaciones que se relacionan correctamente con Insomnio.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Se relaciona principalmente con Ciática / Lumbalgia</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Puede estar asociada a Estrés</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Se relaciona con Dificultad para conciliar el sueño</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Puede estar asociada principalmente a Osteoporosis</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:59:11</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PAT_00008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Varicocele (Apoyo a la salud vascular y reproductiva masculina)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sintoma_Causa_Patologia</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Seleccione las DOS afirmaciones que se relacionan correctamente con Varicocele (Apoyo a la salud vascular y reproductiva masculina).</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Puede estar asociada principalmente a Disfunción sexual masculina / Dificultad para la erección</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Puede estar asociada a Insuficiencia de las válvulas venosas del cordón espermático</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Se relaciona con Diagnóstico médico de varicocele</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Se relaciona principalmente con Perimenopausia / Menopausia</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:59:11</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>P008</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PAT_00009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bienestar íntimo femenino y función sexual</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sintoma_Causa_Patologia</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Seleccione las DOS afirmaciones que se relacionan correctamente con Bienestar íntimo femenino y función sexual.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Puede estar asociada a Disminución de estrógenos (perimenopausia/menopausia)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Puede estar asociada principalmente a Disfunción sexual masculina / Dificultad para la erección</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Se relaciona con Disminución de la libido</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Se relaciona principalmente con Síndrome de Ovario Poliquístico (SOP)</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:59:11</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>P009</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PAT_00010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apoyo a la salud reproductiva femenina y planificación del embarazo</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sintoma_Causa_Patologia</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Seleccione las DOS afirmaciones que se relacionan correctamente con Apoyo a la salud reproductiva femenina y planificación del embarazo.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Se relaciona principalmente con Bienestar íntimo femenino y función sexual</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Se relaciona con Dificultad para lograr embarazo</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Puede estar asociada principalmente a Perimenopausia / Menopausia</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Puede estar asociada a Déficit nutricional (ácido fólico, hierro, zinc, vitamina D)</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:59:11</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>P010</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PAT_00011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Síndrome de Ovario Poliquístico (SOP)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sintoma_Causa_Patologia</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Seleccione las DOS afirmaciones que se relacionan correctamente con Síndrome de Ovario Poliquístico (SOP).</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Se relaciona con Menstruaciones irregulares o ausencia de menstruación</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Puede estar asociada principalmente a Varicocele (Apoyo a la salud vascular y reproductiva masculina)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Se relaciona principalmente con Artritis inflamatoria</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Puede estar asociada a Predisposición genética</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:59:11</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PAT_00012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Quistes ováricos funcionales</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sintoma_Causa_Patologia</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Seleccione las DOS afirmaciones que se relacionan correctamente con Quistes ováricos funcionales.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Se relaciona con Dolor pélvico unilateral</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Puede estar asociada principalmente a Disfunción sexual masculina / Dificultad para la erección</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Puede estar asociada a Cambios normales del ciclo ovulatorio</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Se relaciona principalmente con Salud prostática / Molestias prostáticas</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:59:11</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PAT_00013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Endometriosis</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sintoma_Causa_Patologia</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Seleccione las DOS afirmaciones que se relacionan correctamente con Endometriosis.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Puede estar asociada principalmente a Salud prostática / Molestias prostáticas</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Se relaciona principalmente con Artritis inflamatoria</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Puede estar asociada a Predisposición genética</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Se relaciona con Dolor menstrual intenso</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:59:11</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>P013</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PAT_00014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Osteoporosis</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sintoma_Causa_Patologia</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Seleccione las DOS afirmaciones que se relacionan correctamente con Osteoporosis.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Puede estar asociada principalmente a Síndrome de Ovario Poliquístico (SOP)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Puede estar asociada a Envejecimiento</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Se relaciona principalmente con Salud prostática / Molestias prostáticas</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Se relaciona con Dolor de espalda frecuente</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:59:11</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>P014</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PAT_00015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Artrosis (desgaste articular / osteoartritis)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sintoma_Causa_Patologia</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Seleccione las DOS afirmaciones que se relacionan correctamente con Artrosis (desgaste articular / osteoartritis).</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Puede estar asociada principalmente a Dolor muscular, contracturas y molestias musculoesqueléticas localizadas</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Puede estar asociada a Envejecimiento</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Se relaciona principalmente con Ciática / Lumbalgia</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Se relaciona con Dolor en rodillas, cadera, manos o columna</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:59:11</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>P015</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PAT_00016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Artritis inflamatoria</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sintoma_Causa_Patologia</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Seleccione las DOS afirmaciones que se relacionan correctamente con Artritis inflamatoria.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Se relaciona con Dolor articular</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Se relaciona principalmente con Síndrome de Ovario Poliquístico (SOP)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Puede estar asociada principalmente a Disfunción sexual masculina / Dificultad para la erección</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Puede estar asociada a Alteraciones del sistema inmunológico</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:59:11</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>P016</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PAT_00017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ciática / Lumbalgia</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sintoma_Causa_Patologia</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Seleccione las DOS afirmaciones que se relacionan correctamente con Ciática / Lumbalgia.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Se relaciona principalmente con Bienestar íntimo femenino y función sexual</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Puede estar asociada principalmente a Disfunción sexual masculina / Dificultad para la erección</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Se relaciona con Dolor lumbar</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Puede estar asociada a Sobrecarga física</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:59:11</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>P017</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PAT_00018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Dolor muscular, contracturas y molestias musculoesqueléticas localizadas</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sintoma_Causa_Patologia</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Seleccione las DOS afirmaciones que se relacionan correctamente con Dolor muscular, contracturas y molestias musculoesqueléticas localizadas.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Puede estar asociada principalmente a Disfunción sexual masculina / Dificultad para la erección</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Se relaciona principalmente con Salud prostática / Molestias prostáticas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Puede estar asociada a Esfuerzo físico</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Se relaciona con Dolor localizado</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:59:11</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>P018</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PAT_00019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Fibromialgia</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sintoma_Causa_Patologia</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Seleccione las DOS afirmaciones que se relacionan correctamente con Fibromialgia.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Se relaciona con Dolor generalizado en diferentes zonas del cuerpo</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Puede estar asociada principalmente a Espolón calcáneo / dolor de talón (fascitis plantar asociada)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Puede estar asociada a Alteraciones en la percepción del dolor</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Se relaciona principalmente con Dolor muscular, contracturas y molestias musculoesqueléticas localizadas</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:59:11</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>P019</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PAT_00020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Espolón calcáneo / dolor de talón (fascitis plantar asociada)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sintoma_Causa_Patologia</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Seleccione las DOS afirmaciones que se relacionan correctamente con Espolón calcáneo / dolor de talón (fascitis plantar asociada).</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Se relaciona con Dolor en el talón al dar los primeros pasos</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Puede estar asociada a Sobrecarga del pie</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Se relaciona principalmente con Control glucémico (Diabetes mellitus tipo 2 / Prediabetes)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Puede estar asociada principalmente a Perimenopausia / Menopausia</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:59:11</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>P020</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BANCO_PREGUNTAS_GENERALES.xlsx
+++ b/BANCO_PREGUNTAS_GENERALES.xlsx
@@ -1950,7 +1950,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>

--- a/BANCO_PREGUNTAS_GENERALES.xlsx
+++ b/BANCO_PREGUNTAS_GENERALES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1965,6 +1965,4386 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PAT_00021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Caída de cabello (Alopecia)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Descripcion_Causa</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Considere Caída de cabello (Alopecia). La descripción es: Pérdida de densidad o volumen del cabello; puede ser temporal o progresiva según la causa. y uno de los factores relacionados es Androgenética (DHT). Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>El factor indicado no se relaciona con esta patología.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Una causa o factor relacionado es Androgenética (DHT).</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>La descripción corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Caída de cabello (Alopecia).</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PAT_00022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Caída de cabello (Alopecia)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Descripcion_Sintomas</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Considere la patología Caída de cabello (Alopecia). Su descripción es: Pérdida de densidad o volumen del cabello; puede ser temporal o progresiva según la causa. y presenta señales como Disminución de densidad; entradas; afinamiento; caída difusa; picazón/caspa; cuero cabelludo sensible; cambios en uñas; fatiga.. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Caída de cabello (Alopecia).</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Las señales indicadas son compatibles con Caída de cabello (Alopecia).</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a una condición diferente.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Las señales indicadas no son compatibles con esta patología.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PAT_00023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Caída de cabello (Alopecia)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sintomas_Causa</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>En relación con Caída de cabello (Alopecia), considere la señal Disminución de densidad y el factor Androgenética (DHT). Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Disminución de densidad corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Androgenética (DHT) corresponde exclusivamente a otra patología.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Androgenética (DHT) puede estar relacionada con Caída de cabello (Alopecia).</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Disminución de densidad puede presentarse en Caída de cabello (Alopecia).</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PAT_00024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Salud prostática / Molestias prostáticas</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Descripcion_Sintomas</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Considere la patología Salud prostática / Molestias prostáticas. Su descripción es: Alteraciones de la próstata que pueden afectar la micción, producir inflamación o molestias y, en algunos casos, asociarse con cambios en la función sexual. y presenta señales como Chorro débil; aumento de la frecuencia urinaria; levantarse varias veces en la noche; dificultad para iniciar la micción; sensación de vaciamiento incompleto; goteo postmiccional; ardor al orinar; dolor pélvico; dolor al eyacular; disminución de la libido; dificultad para lograr o mantener la erección.. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a una condición diferente.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Salud prostática / Molestias prostáticas.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Las señales indicadas no son compatibles con esta patología.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Las señales indicadas son compatibles con Salud prostática / Molestias prostáticas.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PAT_00025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Salud prostática / Molestias prostáticas</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Descripcion_Causa</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Considere Salud prostática / Molestias prostáticas. La descripción es: Alteraciones de la próstata que pueden afectar la micción, producir inflamación o molestias y, en algunos casos, asociarse con cambios en la función sexual. y uno de los factores relacionados es Hiperplasia prostática benigna. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Una causa o factor relacionado es Hiperplasia prostática benigna.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Salud prostática / Molestias prostáticas.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>La descripción corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>El factor indicado no se relaciona con esta patología.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PAT_00026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Salud prostática / Molestias prostáticas</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Sintomas_Causa</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>En relación con Salud prostática / Molestias prostáticas, considere la señal Chorro débil y el factor Hiperplasia prostática benigna. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hiperplasia prostática benigna corresponde exclusivamente a otra patología.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Hiperplasia prostática benigna puede estar relacionada con Salud prostática / Molestias prostáticas.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Chorro débil corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Chorro débil puede presentarse en Salud prostática / Molestias prostáticas.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PAT_00027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Disfunción sexual masculina / Dificultad para la erección</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Descripcion_Causa</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Considere Disfunción sexual masculina / Dificultad para la erección. La descripción es: Dificultad persistente para lograr o mantener una erección suficiente para una relación sexual satisfactoria. Puede estar relacionada con factores físicos, hormonales, circulatorios, prostáticos o emocionales. y uno de los factores relacionados es Estrés o ansiedad. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Disfunción sexual masculina / Dificultad para la erección.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>La descripción corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>El factor indicado no se relaciona con esta patología.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Una causa o factor relacionado es Estrés o ansiedad.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>P003</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PAT_00028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Disfunción sexual masculina / Dificultad para la erección</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Descripcion_Sintomas</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Considere la patología Disfunción sexual masculina / Dificultad para la erección. Su descripción es: Dificultad persistente para lograr o mantener una erección suficiente para una relación sexual satisfactoria. Puede estar relacionada con factores físicos, hormonales, circulatorios, prostáticos o emocionales. y presenta señales como Disminución de la libido; dificultad para lograr la erección; dificultad para mantenerla; erecciones menos firmes; disminución del deseo sexual; fatiga.. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Disfunción sexual masculina / Dificultad para la erección.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a una condición diferente.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Las señales indicadas no son compatibles con esta patología.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Las señales indicadas son compatibles con Disfunción sexual masculina / Dificultad para la erección.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>P003</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PAT_00029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Disfunción sexual masculina / Dificultad para la erección</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Sintomas_Causa</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>En relación con Disfunción sexual masculina / Dificultad para la erección, considere la señal Disminución de la libido y el factor Estrés o ansiedad. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Estrés o ansiedad puede estar relacionada con Disfunción sexual masculina / Dificultad para la erección.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Disminución de la libido corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Estrés o ansiedad corresponde exclusivamente a otra patología.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Disminución de la libido puede presentarse en Disfunción sexual masculina / Dificultad para la erección.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>P003</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PAT_00030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Vitalidad masculina y apoyo hormonal (Hipogonadismo / Deficiencia de testosterona*)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Descripcion_Causa</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Considere Vitalidad masculina y apoyo hormonal (Hipogonadismo / Deficiencia de testosterona*). La descripción es: Disminución de la energía, la fuerza, el deseo sexual o el rendimiento físico que puede estar relacionada con la edad, el estilo de vida, deficiencias nutricionales o alteraciones hormonales. y uno de los factores relacionados es Envejecimiento. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>El factor indicado no se relaciona con esta patología.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>La descripción corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Una causa o factor relacionado es Envejecimiento.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Vitalidad masculina y apoyo hormonal (Hipogonadismo / Deficiencia de testosterona*).</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PAT_00031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Vitalidad masculina y apoyo hormonal (Hipogonadismo / Deficiencia de testosterona*)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Sintomas_Causa</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>En relación con Vitalidad masculina y apoyo hormonal (Hipogonadismo / Deficiencia de testosterona*), considere la señal Disminución de la libido y el factor Envejecimiento. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Disminución de la libido corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Disminución de la libido puede presentarse en Vitalidad masculina y apoyo hormonal (Hipogonadismo / Deficiencia de testosterona*).</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Envejecimiento corresponde exclusivamente a otra patología.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Envejecimiento puede estar relacionada con Vitalidad masculina y apoyo hormonal (Hipogonadismo / Deficiencia de testosterona*).</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PAT_00032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Vitalidad masculina y apoyo hormonal (Hipogonadismo / Deficiencia de testosterona*)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Descripcion_Sintomas</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Considere la patología Vitalidad masculina y apoyo hormonal (Hipogonadismo / Deficiencia de testosterona*). Su descripción es: Disminución de la energía, la fuerza, el deseo sexual o el rendimiento físico que puede estar relacionada con la edad, el estilo de vida, deficiencias nutricionales o alteraciones hormonales. y presenta señales como Disminución de la libido; fatiga persistente; pérdida de fuerza; disminución de masa muscular; recuperación lenta después del ejercicio; menor rendimiento físico; aumento de grasa abdominal; disminución de la motivación o vitalidad; erecciones matutinas menos frecuentes.. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Vitalidad masculina y apoyo hormonal (Hipogonadismo / Deficiencia de testosterona*).</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a una condición diferente.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Las señales indicadas no son compatibles con esta patología.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Las señales indicadas son compatibles con Vitalidad masculina y apoyo hormonal (Hipogonadismo / Deficiencia de testosterona*).</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PAT_00033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Control glucémico (Diabetes mellitus tipo 2 / Prediabetes)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Descripcion_Causa</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Considere Control glucémico (Diabetes mellitus tipo 2 / Prediabetes). La descripción es: Alteración del metabolismo de la glucosa que ocasiona niveles elevados de azúcar en sangre o dificultad para mantenerlos dentro de rangos normales. y uno de los factores relacionados es Resistencia a la insulina. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>El factor indicado no se relaciona con esta patología.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Control glucémico (Diabetes mellitus tipo 2 / Prediabetes).</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Una causa o factor relacionado es Resistencia a la insulina.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>La descripción corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PAT_00034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Control glucémico (Diabetes mellitus tipo 2 / Prediabetes)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Descripcion_Sintomas</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Considere la patología Control glucémico (Diabetes mellitus tipo 2 / Prediabetes). Su descripción es: Alteración del metabolismo de la glucosa que ocasiona niveles elevados de azúcar en sangre o dificultad para mantenerlos dentro de rangos normales. y presenta señales como Diagnóstico de diabetes o prediabetes; glucosa elevada; sed excesiva; aumento de la frecuencia urinaria; hambre constante; fatiga; visión borrosa; cicatrización lenta; hormigueo o adormecimiento en manos o pies; infecciones frecuentes; sobrepeso u obesidad abdominal.. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Las señales indicadas son compatibles con Control glucémico (Diabetes mellitus tipo 2 / Prediabetes).</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a una condición diferente.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Control glucémico (Diabetes mellitus tipo 2 / Prediabetes).</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Las señales indicadas no son compatibles con esta patología.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PAT_00035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Control glucémico (Diabetes mellitus tipo 2 / Prediabetes)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Sintomas_Causa</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>En relación con Control glucémico (Diabetes mellitus tipo 2 / Prediabetes), considere la señal Diagnóstico de diabetes o prediabetes y el factor Resistencia a la insulina. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Resistencia a la insulina corresponde exclusivamente a otra patología.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Diagnóstico de diabetes o prediabetes corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Diagnóstico de diabetes o prediabetes puede presentarse en Control glucémico (Diabetes mellitus tipo 2 / Prediabetes).</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Resistencia a la insulina puede estar relacionada con Control glucémico (Diabetes mellitus tipo 2 / Prediabetes).</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PAT_00036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Perimenopausia / Menopausia</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Descripcion_Sintomas</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Considere la patología Perimenopausia / Menopausia. Su descripción es: Etapa de transición hormonal caracterizada por la disminución progresiva de estrógenos, que puede afectar la salud física, emocional, metabólica, ósea, urinaria y sexual de la mujer. y presenta señales como Alteraciones menstruales; sofocos; sudoración nocturna; cambios del estado de ánimo; insomnio; disminución de la libido; resequedad vaginal; aumento de peso; caída del cabello; cambios en la piel; dolor articular; fatiga; infecciones urinarias recurrentes.. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Perimenopausia / Menopausia.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a una condición diferente.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Las señales indicadas no son compatibles con esta patología.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Las señales indicadas son compatibles con Perimenopausia / Menopausia.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PAT_00037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Perimenopausia / Menopausia</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Sintomas_Causa</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>En relación con Perimenopausia / Menopausia, considere la señal Alteraciones menstruales y el factor Disminución fisiológica de estrógenos y progesterona. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alteraciones menstruales corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Disminución fisiológica de estrógenos y progesterona puede estar relacionada con Perimenopausia / Menopausia.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Disminución fisiológica de estrógenos y progesterona corresponde exclusivamente a otra patología.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Alteraciones menstruales puede presentarse en Perimenopausia / Menopausia.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PAT_00038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Perimenopausia / Menopausia</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Descripcion_Causa</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Considere Perimenopausia / Menopausia. La descripción es: Etapa de transición hormonal caracterizada por la disminución progresiva de estrógenos, que puede afectar la salud física, emocional, metabólica, ósea, urinaria y sexual de la mujer. y uno de los factores relacionados es Disminución fisiológica de estrógenos y progesterona. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Una causa o factor relacionado es Disminución fisiológica de estrógenos y progesterona.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Perimenopausia / Menopausia.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>La descripción corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>El factor indicado no se relaciona con esta patología.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PAT_00039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Insomnio</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Descripcion_Causa</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Considere Insomnio. La descripción es: Dificultad para conciliar el sueño, permanecer dormido o lograr un descanso reparador, afectando el bienestar físico, mental y emocional. y uno de los factores relacionados es Estrés. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>El factor indicado no se relaciona con esta patología.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Una causa o factor relacionado es Estrés.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Insomnio.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>La descripción corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PAT_00040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Insomnio</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Sintomas_Causa</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>En relación con Insomnio, considere la señal Dificultad para conciliar el sueño y el factor Estrés. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Estrés puede estar relacionada con Insomnio.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Dificultad para conciliar el sueño corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Estrés corresponde exclusivamente a otra patología.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Dificultad para conciliar el sueño puede presentarse en Insomnio.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PAT_00041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Insomnio</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Descripcion_Sintomas</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Considere la patología Insomnio. Su descripción es: Dificultad para conciliar el sueño, permanecer dormido o lograr un descanso reparador, afectando el bienestar físico, mental y emocional. y presenta señales como Dificultad para conciliar el sueño; despertares frecuentes; despertar muy temprano; sensación de sueño poco reparador; cansancio al despertar; somnolencia diurna; irritabilidad; dificultad para concentrarse; disminución del rendimiento físico o mental; fatiga.. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a una condición diferente.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Las señales indicadas no son compatibles con esta patología.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Las señales indicadas son compatibles con Insomnio.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Insomnio.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PAT_00042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Varicocele (Apoyo a la salud vascular y reproductiva masculina)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Sintomas_Causa</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>En relación con Varicocele (Apoyo a la salud vascular y reproductiva masculina), considere la señal Diagnóstico médico de varicocele y el factor Insuficiencia de las válvulas venosas del cordón espermático. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Diagnóstico médico de varicocele corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Insuficiencia de las válvulas venosas del cordón espermático corresponde exclusivamente a otra patología.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Insuficiencia de las válvulas venosas del cordón espermático puede estar relacionada con Varicocele (Apoyo a la salud vascular y reproductiva masculina).</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Diagnóstico médico de varicocele puede presentarse en Varicocele (Apoyo a la salud vascular y reproductiva masculina).</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>P008</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PAT_00043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Varicocele (Apoyo a la salud vascular y reproductiva masculina)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Descripcion_Causa</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Considere Varicocele (Apoyo a la salud vascular y reproductiva masculina). La descripción es: Dilatación anormal de las venas del cordón espermático, generalmente en el lado izquierdo, que puede afectar la circulación testicular y, en algunos casos, la fertilidad, la producción de testosterona o generar molestias locales. y uno de los factores relacionados es Insuficiencia de las válvulas venosas del cordón espermático. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>La descripción corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Varicocele (Apoyo a la salud vascular y reproductiva masculina).</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Una causa o factor relacionado es Insuficiencia de las válvulas venosas del cordón espermático.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>El factor indicado no se relaciona con esta patología.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>P008</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PAT_00044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Varicocele (Apoyo a la salud vascular y reproductiva masculina)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Descripcion_Sintomas</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Considere la patología Varicocele (Apoyo a la salud vascular y reproductiva masculina). Su descripción es: Dilatación anormal de las venas del cordón espermático, generalmente en el lado izquierdo, que puede afectar la circulación testicular y, en algunos casos, la fertilidad, la producción de testosterona o generar molestias locales. y presenta señales como Diagnóstico médico de varicocele; sensación de pesadez o dolor en el escroto; molestias que aumentan al estar de pie o al realizar esfuerzo; disminución de la fertilidad; disminución de la vitalidad masculina; reducción de las erecciones matutinas; disminución de la libido (en algunos casos).. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Las señales indicadas son compatibles con Varicocele (Apoyo a la salud vascular y reproductiva masculina).</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Las señales indicadas no son compatibles con esta patología.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Varicocele (Apoyo a la salud vascular y reproductiva masculina).</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a una condición diferente.</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>P008</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PAT_00045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Bienestar íntimo femenino y función sexual</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Sintomas_Causa</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>En relación con Bienestar íntimo femenino y función sexual, considere la señal Disminución de la libido y el factor Disminución de estrógenos (perimenopausia/menopausia). Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Disminución de estrógenos (perimenopausia/menopausia) puede estar relacionada con Bienestar íntimo femenino y función sexual.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Disminución de la libido corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Disminución de la libido puede presentarse en Bienestar íntimo femenino y función sexual.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Disminución de estrógenos (perimenopausia/menopausia) corresponde exclusivamente a otra patología.</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>P009</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PAT_00046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Bienestar íntimo femenino y función sexual</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Descripcion_Causa</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Considere Bienestar íntimo femenino y función sexual. La descripción es: Disminución del deseo sexual o alteraciones del bienestar íntimo que pueden afectar la satisfacción durante las relaciones sexuales. Puede estar relacionada con factores hormonales, emocionales, circulatorios, metabólicos o alteraciones de la flora vaginal. y uno de los factores relacionados es Disminución de estrógenos (perimenopausia/menopausia). Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>La descripción corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>El factor indicado no se relaciona con esta patología.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Una causa o factor relacionado es Disminución de estrógenos (perimenopausia/menopausia).</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Bienestar íntimo femenino y función sexual.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>P009</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>PAT_00047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Bienestar íntimo femenino y función sexual</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Descripcion_Sintomas</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Considere la patología Bienestar íntimo femenino y función sexual. Su descripción es: Disminución del deseo sexual o alteraciones del bienestar íntimo que pueden afectar la satisfacción durante las relaciones sexuales. Puede estar relacionada con factores hormonales, emocionales, circulatorios, metabólicos o alteraciones de la flora vaginal. y presenta señales como Disminución de la libido; resequedad vaginal; disminución de la lubricación; molestias o dolor durante las relaciones sexuales; menor sensibilidad o excitación; dificultad para alcanzar el orgasmo; infecciones urinarias o vaginales recurrentes; disminución del bienestar íntimo.. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Las señales indicadas son compatibles con Bienestar íntimo femenino y función sexual.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Las señales indicadas no son compatibles con esta patología.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a una condición diferente.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Bienestar íntimo femenino y función sexual.</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>P009</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PAT_00048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Apoyo a la salud reproductiva femenina y planificación del embarazo</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Descripcion_Causa</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Considere Apoyo a la salud reproductiva femenina y planificación del embarazo. La descripción es: Condición en la que uno o varios factores nutricionales, hormonales, metabólicos, emocionales o de estilo de vida pueden disminuir las condiciones óptimas para la concepción. El sistema brinda apoyo nutricional y bienestar reproductivo como complemento y no reemplaza la valoración médica especializada. y uno de los factores relacionados es Déficit nutricional (ácido fólico, hierro, zinc, vitamina D). Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>La descripción corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Apoyo a la salud reproductiva femenina y planificación del embarazo.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>El factor indicado no se relaciona con esta patología.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Una causa o factor relacionado es Déficit nutricional (ácido fólico, hierro, zinc, vitamina D).</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>P010</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PAT_00049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Apoyo a la salud reproductiva femenina y planificación del embarazo</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Sintomas_Causa</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>En relación con Apoyo a la salud reproductiva femenina y planificación del embarazo, considere la señal Dificultad para lograr embarazo y el factor Déficit nutricional (ácido fólico, hierro, zinc, vitamina D). Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Déficit nutricional (ácido fólico, hierro, zinc, vitamina D) corresponde exclusivamente a otra patología.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Déficit nutricional (ácido fólico, hierro, zinc, vitamina D) puede estar relacionada con Apoyo a la salud reproductiva femenina y planificación del embarazo.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Dificultad para lograr embarazo puede presentarse en Apoyo a la salud reproductiva femenina y planificación del embarazo.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Dificultad para lograr embarazo corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>P010</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>PAT_00050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Apoyo a la salud reproductiva femenina y planificación del embarazo</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Descripcion_Sintomas</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Considere la patología Apoyo a la salud reproductiva femenina y planificación del embarazo. Su descripción es: Condición en la que uno o varios factores nutricionales, hormonales, metabólicos, emocionales o de estilo de vida pueden disminuir las condiciones óptimas para la concepción. El sistema brinda apoyo nutricional y bienestar reproductivo como complemento y no reemplaza la valoración médica especializada. y presenta señales como Dificultad para lograr embarazo; planificación del embarazo; ciclos menstruales irregulares; antecedentes de infertilidad; fatiga o deficiencias nutricionales; diagnóstico de baja reserva ovárica o alteraciones ovulatorias; antecedentes de aborto temprano; deseo de optimizar el estado nutricional antes de la concepción.. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Las señales indicadas no son compatibles con esta patología.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a una condición diferente.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Las señales indicadas son compatibles con Apoyo a la salud reproductiva femenina y planificación del embarazo.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Apoyo a la salud reproductiva femenina y planificación del embarazo.</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>P010</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>PAT_00051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Síndrome de Ovario Poliquístico (SOP)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Descripcion_Causa</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Considere Síndrome de Ovario Poliquístico (SOP). La descripción es: Trastorno hormonal y metabólico caracterizado por alteraciones en la ovulación, exceso de andrógenos y, con frecuencia, resistencia a la insulina, que puede afectar la salud reproductiva, metabólica y cardiovascular de la mujer. y uno de los factores relacionados es Predisposición genética. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Síndrome de Ovario Poliquístico (SOP).</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>El factor indicado no se relaciona con esta patología.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Una causa o factor relacionado es Predisposición genética.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>La descripción corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PAT_00052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Síndrome de Ovario Poliquístico (SOP)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Descripcion_Sintomas</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Considere la patología Síndrome de Ovario Poliquístico (SOP). Su descripción es: Trastorno hormonal y metabólico caracterizado por alteraciones en la ovulación, exceso de andrógenos y, con frecuencia, resistencia a la insulina, que puede afectar la salud reproductiva, metabólica y cardiovascular de la mujer. y presenta señales como Menstruaciones irregulares o ausencia de menstruación; dificultad para quedar embarazada; acné; exceso de vello corporal o facial; caída del cabello; aumento de peso; resistencia a la insulina; ovarios con múltiples folículos en ecografía.. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Las señales indicadas no son compatibles con esta patología.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Las señales indicadas son compatibles con Síndrome de Ovario Poliquístico (SOP).</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a una condición diferente.</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Síndrome de Ovario Poliquístico (SOP).</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PAT_00053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Síndrome de Ovario Poliquístico (SOP)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Sintomas_Causa</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>En relación con Síndrome de Ovario Poliquístico (SOP), considere la señal Menstruaciones irregulares o ausencia de menstruación y el factor Predisposición genética. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Menstruaciones irregulares o ausencia de menstruación puede presentarse en Síndrome de Ovario Poliquístico (SOP).</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Predisposición genética puede estar relacionada con Síndrome de Ovario Poliquístico (SOP).</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Predisposición genética corresponde exclusivamente a otra patología.</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Menstruaciones irregulares o ausencia de menstruación corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PAT_00054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Quistes ováricos funcionales</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Descripcion_Causa</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Considere Quistes ováricos funcionales. La descripción es: Presencia de quistes benignos que se forman durante el ciclo menstrual y que, en la mayoría de los casos, desaparecen espontáneamente, aunque algunos pueden producir dolor o alteraciones menstruales. y uno de los factores relacionados es Cambios normales del ciclo ovulatorio. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Una causa o factor relacionado es Cambios normales del ciclo ovulatorio.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Quistes ováricos funcionales.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>El factor indicado no se relaciona con esta patología.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>La descripción corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>PAT_00055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Quistes ováricos funcionales</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Descripcion_Sintomas</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Considere la patología Quistes ováricos funcionales. Su descripción es: Presencia de quistes benignos que se forman durante el ciclo menstrual y que, en la mayoría de los casos, desaparecen espontáneamente, aunque algunos pueden producir dolor o alteraciones menstruales. y presenta señales como Dolor pélvico unilateral; sensación de presión o pesadez en la pelvis; dolor durante las relaciones sexuales; alteraciones del ciclo menstrual; distensión abdominal; en muchos casos ausencia de síntomas.. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a una condición diferente.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Quistes ováricos funcionales.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Las señales indicadas son compatibles con Quistes ováricos funcionales.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Las señales indicadas no son compatibles con esta patología.</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>PAT_00056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Quistes ováricos funcionales</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Sintomas_Causa</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>En relación con Quistes ováricos funcionales, considere la señal Dolor pélvico unilateral y el factor Cambios normales del ciclo ovulatorio. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Dolor pélvico unilateral corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Cambios normales del ciclo ovulatorio corresponde exclusivamente a otra patología.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Dolor pélvico unilateral puede presentarse en Quistes ováricos funcionales.</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Cambios normales del ciclo ovulatorio puede estar relacionada con Quistes ováricos funcionales.</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>PAT_00057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Endometriosis</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Sintomas_Causa</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>En relación con Endometriosis, considere la señal Dolor menstrual intenso y el factor Predisposición genética. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Dolor menstrual intenso corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Dolor menstrual intenso puede presentarse en Endometriosis.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Predisposición genética puede estar relacionada con Endometriosis.</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Predisposición genética corresponde exclusivamente a otra patología.</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>P013</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>PAT_00058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Endometriosis</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Descripcion_Causa</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Considere Endometriosis. La descripción es: Enfermedad inflamatoria crónica en la que tejido similar al endometrio crece fuera del útero, ocasionando dolor pélvico, inflamación y, en algunas mujeres, dificultades para lograr el embarazo. y uno de los factores relacionados es Predisposición genética. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Una causa o factor relacionado es Predisposición genética.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>La descripción corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>El factor indicado no se relaciona con esta patología.</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Endometriosis.</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>P013</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>PAT_00059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Endometriosis</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Descripcion_Sintomas</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Considere la patología Endometriosis. Su descripción es: Enfermedad inflamatoria crónica en la que tejido similar al endometrio crece fuera del útero, ocasionando dolor pélvico, inflamación y, en algunas mujeres, dificultades para lograr el embarazo. y presenta señales como Dolor menstrual intenso; dolor pélvico crónico; dolor durante las relaciones sexuales; sangrado menstrual abundante o prolongado; dolor al evacuar o al orinar durante la menstruación; infertilidad; fatiga.. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Las señales indicadas son compatibles con Endometriosis.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Endometriosis.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a una condición diferente.</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Las señales indicadas no son compatibles con esta patología.</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>P013</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>PAT_00060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Osteoporosis</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Sintomas_Causa</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>En relación con Osteoporosis, considere la señal Dolor de espalda frecuente y el factor Envejecimiento. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Dolor de espalda frecuente corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Envejecimiento puede estar relacionada con Osteoporosis.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Dolor de espalda frecuente puede presentarse en Osteoporosis.</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Envejecimiento corresponde exclusivamente a otra patología.</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>P014</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>PAT_00061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Osteoporosis</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Descripcion_Causa</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Considere Osteoporosis. La descripción es: Enfermedad en la que los huesos pierden densidad y resistencia, aumentando el riesgo de fracturas, especialmente en columna, cadera y muñeca. Puede avanzar silenciosamente durante años sin síntomas evidentes. y uno de los factores relacionados es Envejecimiento. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>El factor indicado no se relaciona con esta patología.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Una causa o factor relacionado es Envejecimiento.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Osteoporosis.</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>La descripción corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>P014</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PAT_00062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Osteoporosis</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Descripcion_Sintomas</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Considere la patología Osteoporosis. Su descripción es: Enfermedad en la que los huesos pierden densidad y resistencia, aumentando el riesgo de fracturas, especialmente en columna, cadera y muñeca. Puede avanzar silenciosamente durante años sin síntomas evidentes. y presenta señales como Dolor de espalda frecuente; pérdida de estatura con los años; postura encorvada; fracturas ante golpes leves; debilidad muscular; disminución de fuerza; dificultad para mantener actividad física; antecedentes familiares de osteoporosis; menopausia o edad avanzada.. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Osteoporosis.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Las señales indicadas son compatibles con Osteoporosis.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a una condición diferente.</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Las señales indicadas no son compatibles con esta patología.</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>P014</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>PAT_00063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Artrosis (desgaste articular / osteoartritis)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Descripcion_Causa</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Considere Artrosis (desgaste articular / osteoartritis). La descripción es: Enfermedad degenerativa de las articulaciones en la que el cartílago que protege los huesos se deteriora progresivamente, generando dolor, rigidez y pérdida de movilidad. y uno de los factores relacionados es Envejecimiento. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>El factor indicado no se relaciona con esta patología.</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Artrosis (desgaste articular / osteoartritis).</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>La descripción corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Una causa o factor relacionado es Envejecimiento.</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>P015</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>PAT_00064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Artrosis (desgaste articular / osteoartritis)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Descripcion_Sintomas</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Considere la patología Artrosis (desgaste articular / osteoartritis). Su descripción es: Enfermedad degenerativa de las articulaciones en la que el cartílago que protege los huesos se deteriora progresivamente, generando dolor, rigidez y pérdida de movilidad. y presenta señales como Dolor en rodillas, cadera, manos o columna; rigidez después del reposo; dificultad para movilizar la articulación; crujidos o sensación de roce; disminución de movilidad; molestias que aumentan con el uso de la articulación.. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a una condición diferente.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Las señales indicadas no son compatibles con esta patología.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Artrosis (desgaste articular / osteoartritis).</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Las señales indicadas son compatibles con Artrosis (desgaste articular / osteoartritis).</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>P015</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PAT_00065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Artrosis (desgaste articular / osteoartritis)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Sintomas_Causa</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>En relación con Artrosis (desgaste articular / osteoartritis), considere la señal Dolor en rodillas, cadera, manos o columna y el factor Envejecimiento. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Envejecimiento corresponde exclusivamente a otra patología.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Dolor en rodillas, cadera, manos o columna puede presentarse en Artrosis (desgaste articular / osteoartritis).</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Envejecimiento puede estar relacionada con Artrosis (desgaste articular / osteoartritis).</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Dolor en rodillas, cadera, manos o columna corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>P015</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>PAT_00066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Artritis inflamatoria</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Sintomas_Causa</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>En relación con Artritis inflamatoria, considere la señal Dolor articular y el factor Alteraciones del sistema inmunológico. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Dolor articular corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Alteraciones del sistema inmunológico puede estar relacionada con Artritis inflamatoria.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Alteraciones del sistema inmunológico corresponde exclusivamente a otra patología.</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Dolor articular puede presentarse en Artritis inflamatoria.</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>P016</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>PAT_00067</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Artritis inflamatoria</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Descripcion_Sintomas</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Considere la patología Artritis inflamatoria. Su descripción es: Condición en la que existe inflamación dentro de una o varias articulaciones, causando dolor, rigidez y sensibilidad. Algunas formas pueden tener origen autoinmune y requieren seguimiento médico. y presenta señales como Dolor articular; inflamación visible; articulaciones calientes o sensibles; rigidez prolongada especialmente al despertar; dificultad para mover la articulación; fatiga asociada; molestias en varias articulaciones.. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Artritis inflamatoria.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a una condición diferente.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Las señales indicadas no son compatibles con esta patología.</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Las señales indicadas son compatibles con Artritis inflamatoria.</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>P016</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>PAT_00068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Artritis inflamatoria</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Descripcion_Causa</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Considere Artritis inflamatoria. La descripción es: Condición en la que existe inflamación dentro de una o varias articulaciones, causando dolor, rigidez y sensibilidad. Algunas formas pueden tener origen autoinmune y requieren seguimiento médico. y uno de los factores relacionados es Alteraciones del sistema inmunológico. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Artritis inflamatoria.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>El factor indicado no se relaciona con esta patología.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Una causa o factor relacionado es Alteraciones del sistema inmunológico.</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>La descripción corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>P016</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>PAT_00069</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ciática / Lumbalgia</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Sintomas_Causa</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>En relación con Ciática / Lumbalgia, considere la señal Dolor lumbar y el factor Sobrecarga física. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Dolor lumbar corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sobrecarga física corresponde exclusivamente a otra patología.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Sobrecarga física puede estar relacionada con Ciática / Lumbalgia.</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Dolor lumbar puede presentarse en Ciática / Lumbalgia.</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>P017</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>PAT_00070</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ciática / Lumbalgia</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Descripcion_Causa</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Considere Ciática / Lumbalgia. La descripción es: Dolor localizado en la zona lumbar que puede relacionarse con músculos, columna o irritación del nervio ciático, pudiendo extenderse hacia glúteo o pierna. y uno de los factores relacionados es Sobrecarga física. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Ciática / Lumbalgia.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>La descripción corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Una causa o factor relacionado es Sobrecarga física.</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>El factor indicado no se relaciona con esta patología.</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>P017</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>PAT_00071</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ciática / Lumbalgia</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Descripcion_Sintomas</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Considere la patología Ciática / Lumbalgia. Su descripción es: Dolor localizado en la zona lumbar que puede relacionarse con músculos, columna o irritación del nervio ciático, pudiendo extenderse hacia glúteo o pierna. y presenta señales como Dolor lumbar; dolor que baja hacia glúteo o pierna; sensación de tirón; rigidez de espalda; dificultad para moverse; molestias después de permanecer mucho tiempo sentado o de pie.. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Las señales indicadas son compatibles con Ciática / Lumbalgia.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a una condición diferente.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Ciática / Lumbalgia.</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Las señales indicadas no son compatibles con esta patología.</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>P017</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>PAT_00072</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Dolor muscular, contracturas y molestias musculoesqueléticas localizadas</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Descripcion_Sintomas</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Considere la patología Dolor muscular, contracturas y molestias musculoesqueléticas localizadas. Su descripción es: Molestias relacionadas con tensión, sobrecarga o irritación de músculos y tejidos blandos, que pueden afectar cuello, espalda u otras zonas del cuerpo. y presenta señales como Dolor localizado; sensación de tensión o contractura; rigidez muscular; molestias al mover la zona; cuello o espalda cargados; sensación de cansancio muscular.. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Dolor muscular, contracturas y molestias musculoesqueléticas localizadas.</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Las señales indicadas son compatibles con Dolor muscular, contracturas y molestias musculoesqueléticas localizadas.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Las señales indicadas no son compatibles con esta patología.</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a una condición diferente.</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>P018</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>PAT_00073</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Dolor muscular, contracturas y molestias musculoesqueléticas localizadas</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Sintomas_Causa</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>En relación con Dolor muscular, contracturas y molestias musculoesqueléticas localizadas, considere la señal Dolor localizado y el factor Esfuerzo físico. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Dolor localizado corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Esfuerzo físico corresponde exclusivamente a otra patología.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Esfuerzo físico puede estar relacionada con Dolor muscular, contracturas y molestias musculoesqueléticas localizadas.</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Dolor localizado puede presentarse en Dolor muscular, contracturas y molestias musculoesqueléticas localizadas.</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>P018</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>PAT_00074</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Dolor muscular, contracturas y molestias musculoesqueléticas localizadas</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Descripcion_Causa</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Considere Dolor muscular, contracturas y molestias musculoesqueléticas localizadas. La descripción es: Molestias relacionadas con tensión, sobrecarga o irritación de músculos y tejidos blandos, que pueden afectar cuello, espalda u otras zonas del cuerpo. y uno de los factores relacionados es Esfuerzo físico. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Dolor muscular, contracturas y molestias musculoesqueléticas localizadas.</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Una causa o factor relacionado es Esfuerzo físico.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>La descripción corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>El factor indicado no se relaciona con esta patología.</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>P018</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>PAT_00075</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Fibromialgia</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Sintomas_Causa</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>En relación con Fibromialgia, considere la señal Dolor generalizado en diferentes zonas del cuerpo y el factor Alteraciones en la percepción del dolor. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Alteraciones en la percepción del dolor puede estar relacionada con Fibromialgia.</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Alteraciones en la percepción del dolor corresponde exclusivamente a otra patología.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Dolor generalizado en diferentes zonas del cuerpo puede presentarse en Fibromialgia.</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Dolor generalizado en diferentes zonas del cuerpo corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>P019</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>PAT_00076</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Fibromialgia</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Descripcion_Sintomas</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Considere la patología Fibromialgia. Su descripción es: Síndrome caracterizado por dolor musculoesquelético generalizado, acompañado frecuentemente de fatiga, alteraciones del sueño y mayor sensibilidad al dolor. y presenta señales como Dolor generalizado en diferentes zonas del cuerpo; cansancio frecuente; sueño no reparador; rigidez; sensibilidad aumentada; dificultad para concentrarse; molestias musculares persistentes.. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Las señales indicadas son compatibles con Fibromialgia.</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a una condición diferente.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Fibromialgia.</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Las señales indicadas no son compatibles con esta patología.</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>P019</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>PAT_00077</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Fibromialgia</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Descripcion_Causa</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Considere Fibromialgia. La descripción es: Síndrome caracterizado por dolor musculoesquelético generalizado, acompañado frecuentemente de fatiga, alteraciones del sueño y mayor sensibilidad al dolor. y uno de los factores relacionados es Alteraciones en la percepción del dolor. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Fibromialgia.</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>El factor indicado no se relaciona con esta patología.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Una causa o factor relacionado es Alteraciones en la percepción del dolor.</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>La descripción corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>P019</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>PAT_00078</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Espolón calcáneo / dolor de talón (fascitis plantar asociada)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Sintomas_Causa</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>En relación con Espolón calcáneo / dolor de talón (fascitis plantar asociada), considere la señal Dolor en el talón al dar los primeros pasos y el factor Sobrecarga del pie. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Dolor en el talón al dar los primeros pasos corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Sobrecarga del pie puede estar relacionada con Espolón calcáneo / dolor de talón (fascitis plantar asociada).</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Sobrecarga del pie corresponde exclusivamente a otra patología.</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Dolor en el talón al dar los primeros pasos puede presentarse en Espolón calcáneo / dolor de talón (fascitis plantar asociada).</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>P020</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>PAT_00079</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Espolón calcáneo / dolor de talón (fascitis plantar asociada)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Descripcion_Sintomas</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Considere la patología Espolón calcáneo / dolor de talón (fascitis plantar asociada). Su descripción es: Molestia localizada en la zona del talón que suele relacionarse con irritación de tejidos de soporte del pie y puede generar dolor al caminar o permanecer de pie. y presenta señales como Dolor en el talón al dar los primeros pasos; dolor después de periodos de descanso; sensibilidad al apoyar; molestia al caminar; rigidez en la planta del pie.. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Espolón calcáneo / dolor de talón (fascitis plantar asociada).</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Las señales indicadas son compatibles con Espolón calcáneo / dolor de talón (fascitis plantar asociada).</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a una condición diferente.</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Las señales indicadas no son compatibles con esta patología.</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>P020</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>PAT_00080</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Espolón calcáneo / dolor de talón (fascitis plantar asociada)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Descripcion_Causa</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Considere Espolón calcáneo / dolor de talón (fascitis plantar asociada). La descripción es: Molestia localizada en la zona del talón que suele relacionarse con irritación de tejidos de soporte del pie y puede generar dolor al caminar o permanecer de pie. y uno de los factores relacionados es Sobrecarga del pie. Seleccione las DOS afirmaciones correctas.</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Una causa o factor relacionado es Sobrecarga del pie.</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>El factor indicado no se relaciona con esta patología.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>La descripción corresponde a Espolón calcáneo / dolor de talón (fascitis plantar asociada).</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>La descripción corresponde principalmente a otra condición.</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:51</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>P020</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BANCO_PREGUNTAS_GENERALES.xlsx
+++ b/BANCO_PREGUNTAS_GENERALES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O81"/>
+  <dimension ref="A1:O161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6345,6 +6345,5846 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>PAT_00081</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Caída de cabello (Alopecia)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Patologia_Descripcion</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>¿Cuál de las siguientes descripciones corresponde a Caída de cabello (Alopecia)?</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Disminución del deseo sexual o alteraciones del bienestar íntimo que pueden afectar la satisfacción durante las relaciones sexuales. Puede estar relacionada con factores hormonales, emocionales, circulatorios, metabólicos o alteraciones de la flora vaginal.</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Molestias relacionadas con tensión, sobrecarga o irritación de músculos y tejidos blandos, que pueden afectar cuello, espalda u otras zonas del cuerpo.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Pérdida de densidad o volumen del cabello; puede ser temporal o progresiva según la causa.</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Dificultad para conciliar el sueño, permanecer dormido o lograr un descanso reparador, afectando el bienestar físico, mental y emocional.</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>PAT_00082</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Caída de cabello (Alopecia)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Descripcion_Patologia</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Una persona presenta la siguiente descripción: Pérdida de densidad o volumen del cabello; puede ser temporal o progresiva según la causa. ¿A cuál de las siguientes patologías corresponde?</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Apoyo a la salud reproductiva femenina y planificación del embarazo</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Perimenopausia / Menopausia</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Caída de cabello (Alopecia)</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Dolor muscular, contracturas y molestias musculoesqueléticas localizadas</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>PAT_00083</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Caída de cabello (Alopecia)</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Sintomas_Patologia</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Una persona presenta señales como Disminución de densidad; entradas; afinamiento; caída difusa; picazón/caspa; cuero cabelludo sensible; cambios en uñas; fatiga.. ¿Con cuál de las siguientes patologías se relacionan?</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Insomnio</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Caída de cabello (Alopecia)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Quistes ováricos funcionales</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Fibromialgia</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>PAT_00084</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Caída de cabello (Alopecia)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Causas_Patologia</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Factores como Androgenética (DHT); déficit nutricional (hierro/zinc/biotina/proteína); estrés y alteración del sueño; postparto; perimenopausia/menopausia; cuero cabelludo (caspa/dermatitis); fármacos/quimio; químicos/cosméticos; tiroides. pueden estar relacionados con cuál de las siguientes patologías?</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Bienestar íntimo femenino y función sexual</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Síndrome de Ovario Poliquístico (SOP)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Fibromialgia</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Caída de cabello (Alopecia)</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>PAT_00085</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Salud prostática / Molestias prostáticas</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Patologia_Descripcion</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>¿Cuál de las siguientes descripciones corresponde a Salud prostática / Molestias prostáticas?</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Etapa de transición hormonal caracterizada por la disminución progresiva de estrógenos, que puede afectar la salud física, emocional, metabólica, ósea, urinaria y sexual de la mujer.</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Enfermedad en la que los huesos pierden densidad y resistencia, aumentando el riesgo de fracturas, especialmente en columna, cadera y muñeca. Puede avanzar silenciosamente durante años sin síntomas evidentes.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Síndrome caracterizado por dolor musculoesquelético generalizado, acompañado frecuentemente de fatiga, alteraciones del sueño y mayor sensibilidad al dolor.</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Alteraciones de la próstata que pueden afectar la micción, producir inflamación o molestias y, en algunos casos, asociarse con cambios en la función sexual.</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>PAT_00086</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Salud prostática / Molestias prostáticas</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Sintomas_Patologia</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Una persona presenta señales como Chorro débil; aumento de la frecuencia urinaria; levantarse varias veces en la noche; dificultad para iniciar la micción; sensación de vaciamiento incompleto; goteo postmiccional; ardor al orinar; dolor pélvico; dolor al eyacular; disminución de la libido; dificultad para lograr o mantener la erección.. ¿Con cuál de las siguientes patologías se relacionan?</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Fibromialgia</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Salud prostática / Molestias prostáticas</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Control glucémico (Diabetes mellitus tipo 2 / Prediabetes)</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Varicocele (Apoyo a la salud vascular y reproductiva masculina)</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>PAT_00087</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Salud prostática / Molestias prostáticas</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Descripcion_Patologia</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Una persona presenta la siguiente descripción: Alteraciones de la próstata que pueden afectar la micción, producir inflamación o molestias y, en algunos casos, asociarse con cambios en la función sexual. ¿A cuál de las siguientes patologías corresponde?</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Artrosis (desgaste articular / osteoartritis)</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Fibromialgia</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Espolón calcáneo / dolor de talón (fascitis plantar asociada)</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Salud prostática / Molestias prostáticas</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>PAT_00088</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Salud prostática / Molestias prostáticas</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Causas_Patologia</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Factores como Hiperplasia prostática benigna; prostatitis; predisposición genética; cambios hormonales; obesidad; infecciones urinarias; envejecimiento. pueden estar relacionados con cuál de las siguientes patologías?</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Varicocele (Apoyo a la salud vascular y reproductiva masculina)</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Salud prostática / Molestias prostáticas</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Espolón calcáneo / dolor de talón (fascitis plantar asociada)</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Disfunción sexual masculina / Dificultad para la erección</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>PAT_00089</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Disfunción sexual masculina / Dificultad para la erección</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Descripcion_Patologia</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Una persona presenta la siguiente descripción: Dificultad persistente para lograr o mantener una erección suficiente para una relación sexual satisfactoria. Puede estar relacionada con factores físicos, hormonales, circulatorios, prostáticos o emocionales. ¿A cuál de las siguientes patologías corresponde?</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Espolón calcáneo / dolor de talón (fascitis plantar asociada)</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Disfunción sexual masculina / Dificultad para la erección</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Vitalidad masculina y apoyo hormonal (Hipogonadismo / Deficiencia de testosterona*)</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Perimenopausia / Menopausia</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>P003</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>PAT_00090</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Disfunción sexual masculina / Dificultad para la erección</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Patologia_Descripcion</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>¿Cuál de las siguientes descripciones corresponde a Disfunción sexual masculina / Dificultad para la erección?</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Dificultad persistente para lograr o mantener una erección suficiente para una relación sexual satisfactoria. Puede estar relacionada con factores físicos, hormonales, circulatorios, prostáticos o emocionales.</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Molestia localizada en la zona del talón que suele relacionarse con irritación de tejidos de soporte del pie y puede generar dolor al caminar o permanecer de pie.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Molestias relacionadas con tensión, sobrecarga o irritación de músculos y tejidos blandos, que pueden afectar cuello, espalda u otras zonas del cuerpo.</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Condición en la que existe inflamación dentro de una o varias articulaciones, causando dolor, rigidez y sensibilidad. Algunas formas pueden tener origen autoinmune y requieren seguimiento médico.</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>P003</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>PAT_00091</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Disfunción sexual masculina / Dificultad para la erección</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Causas_Patologia</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Factores como Estrés o ansiedad; alteraciones vasculares; hipertensión; sobrepeso u obesidad; problemas prostáticos; disminución de testosterona asociada a la edad; sedentarismo; algunos medicamentos; diabetes; tabaquismo. pueden estar relacionados con cuál de las siguientes patologías?</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Caída de cabello (Alopecia)</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Disfunción sexual masculina / Dificultad para la erección</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Endometriosis</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Perimenopausia / Menopausia</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>P003</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>PAT_00092</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Disfunción sexual masculina / Dificultad para la erección</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Sintomas_Patologia</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Una persona presenta señales como Disminución de la libido; dificultad para lograr la erección; dificultad para mantenerla; erecciones menos firmes; disminución del deseo sexual; fatiga.. ¿Con cuál de las siguientes patologías se relacionan?</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Salud prostática / Molestias prostáticas</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Apoyo a la salud reproductiva femenina y planificación del embarazo</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Bienestar íntimo femenino y función sexual</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Disfunción sexual masculina / Dificultad para la erección</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>P003</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>PAT_00093</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Vitalidad masculina y apoyo hormonal (Hipogonadismo / Deficiencia de testosterona*)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Patologia_Descripcion</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>¿Cuál de las siguientes descripciones corresponde a Vitalidad masculina y apoyo hormonal (Hipogonadismo / Deficiencia de testosterona*)?</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Disminución de la energía, la fuerza, el deseo sexual o el rendimiento físico que puede estar relacionada con la edad, el estilo de vida, deficiencias nutricionales o alteraciones hormonales.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Síndrome caracterizado por dolor musculoesquelético generalizado, acompañado frecuentemente de fatiga, alteraciones del sueño y mayor sensibilidad al dolor.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Enfermedad en la que los huesos pierden densidad y resistencia, aumentando el riesgo de fracturas, especialmente en columna, cadera y muñeca. Puede avanzar silenciosamente durante años sin síntomas evidentes.</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Molestias relacionadas con tensión, sobrecarga o irritación de músculos y tejidos blandos, que pueden afectar cuello, espalda u otras zonas del cuerpo.</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>PAT_00094</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Vitalidad masculina y apoyo hormonal (Hipogonadismo / Deficiencia de testosterona*)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Descripcion_Patologia</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Una persona presenta la siguiente descripción: Disminución de la energía, la fuerza, el deseo sexual o el rendimiento físico que puede estar relacionada con la edad, el estilo de vida, deficiencias nutricionales o alteraciones hormonales. ¿A cuál de las siguientes patologías corresponde?</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Vitalidad masculina y apoyo hormonal (Hipogonadismo / Deficiencia de testosterona*)</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Perimenopausia / Menopausia</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Espolón calcáneo / dolor de talón (fascitis plantar asociada)</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Caída de cabello (Alopecia)</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>PAT_00095</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Vitalidad masculina y apoyo hormonal (Hipogonadismo / Deficiencia de testosterona*)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Sintomas_Patologia</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Una persona presenta señales como Disminución de la libido; fatiga persistente; pérdida de fuerza; disminución de masa muscular; recuperación lenta después del ejercicio; menor rendimiento físico; aumento de grasa abdominal; disminución de la motivación o vitalidad; erecciones matutinas menos frecuentes.. ¿Con cuál de las siguientes patologías se relacionan?</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Vitalidad masculina y apoyo hormonal (Hipogonadismo / Deficiencia de testosterona*)</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Quistes ováricos funcionales</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Endometriosis</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Perimenopausia / Menopausia</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>PAT_00096</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Vitalidad masculina y apoyo hormonal (Hipogonadismo / Deficiencia de testosterona*)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Causas_Patologia</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Factores como Envejecimiento; estrés crónico; sedentarismo; sobrepeso u obesidad; déficit de zinc u otros nutrientes; mala alimentación; enfermedades metabólicas (diabetes, resistencia a la insulina); disminución fisiológica de testosterona asociada a la edad; hipogonadismo (diagnóstico médico). pueden estar relacionados con cuál de las siguientes patologías?</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Insomnio</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Varicocele (Apoyo a la salud vascular y reproductiva masculina)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Vitalidad masculina y apoyo hormonal (Hipogonadismo / Deficiencia de testosterona*)</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Perimenopausia / Menopausia</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>PAT_00097</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Control glucémico (Diabetes mellitus tipo 2 / Prediabetes)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Patologia_Descripcion</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>¿Cuál de las siguientes descripciones corresponde a Control glucémico (Diabetes mellitus tipo 2 / Prediabetes)?</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Alteración del metabolismo de la glucosa que ocasiona niveles elevados de azúcar en sangre o dificultad para mantenerlos dentro de rangos normales.</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Presencia de quistes benignos que se forman durante el ciclo menstrual y que, en la mayoría de los casos, desaparecen espontáneamente, aunque algunos pueden producir dolor o alteraciones menstruales.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Dolor localizado en la zona lumbar que puede relacionarse con músculos, columna o irritación del nervio ciático, pudiendo extenderse hacia glúteo o pierna.</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Trastorno hormonal y metabólico caracterizado por alteraciones en la ovulación, exceso de andrógenos y, con frecuencia, resistencia a la insulina, que puede afectar la salud reproductiva, metabólica y cardiovascular de la mujer.</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>PAT_00098</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Control glucémico (Diabetes mellitus tipo 2 / Prediabetes)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Causas_Patologia</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Factores como Resistencia a la insulina; predisposición genética; sobrepeso u obesidad; sedentarismo; alimentación rica en azúcares y carbohidratos refinados; síndrome metabólico; estrés crónico; envejecimiento. pueden estar relacionados con cuál de las siguientes patologías?</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Perimenopausia / Menopausia</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Dolor muscular, contracturas y molestias musculoesqueléticas localizadas</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Artrosis (desgaste articular / osteoartritis)</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Control glucémico (Diabetes mellitus tipo 2 / Prediabetes)</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>PAT_00099</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Control glucémico (Diabetes mellitus tipo 2 / Prediabetes)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Sintomas_Patologia</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Una persona presenta señales como Diagnóstico de diabetes o prediabetes; glucosa elevada; sed excesiva; aumento de la frecuencia urinaria; hambre constante; fatiga; visión borrosa; cicatrización lenta; hormigueo o adormecimiento en manos o pies; infecciones frecuentes; sobrepeso u obesidad abdominal.. ¿Con cuál de las siguientes patologías se relacionan?</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Artrosis (desgaste articular / osteoartritis)</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Caída de cabello (Alopecia)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Endometriosis</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Control glucémico (Diabetes mellitus tipo 2 / Prediabetes)</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>PAT_00100</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Control glucémico (Diabetes mellitus tipo 2 / Prediabetes)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Descripcion_Patologia</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Una persona presenta la siguiente descripción: Alteración del metabolismo de la glucosa que ocasiona niveles elevados de azúcar en sangre o dificultad para mantenerlos dentro de rangos normales. ¿A cuál de las siguientes patologías corresponde?</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Varicocele (Apoyo a la salud vascular y reproductiva masculina)</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Dolor muscular, contracturas y molestias musculoesqueléticas localizadas</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Artrosis (desgaste articular / osteoartritis)</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Control glucémico (Diabetes mellitus tipo 2 / Prediabetes)</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>PAT_00101</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Perimenopausia / Menopausia</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Descripcion_Patologia</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Una persona presenta la siguiente descripción: Etapa de transición hormonal caracterizada por la disminución progresiva de estrógenos, que puede afectar la salud física, emocional, metabólica, ósea, urinaria y sexual de la mujer. ¿A cuál de las siguientes patologías corresponde?</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Perimenopausia / Menopausia</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Fibromialgia</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Disfunción sexual masculina / Dificultad para la erección</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Espolón calcáneo / dolor de talón (fascitis plantar asociada)</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>PAT_00102</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Perimenopausia / Menopausia</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Patologia_Descripcion</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>¿Cuál de las siguientes descripciones corresponde a Perimenopausia / Menopausia?</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Trastorno hormonal y metabólico caracterizado por alteraciones en la ovulación, exceso de andrógenos y, con frecuencia, resistencia a la insulina, que puede afectar la salud reproductiva, metabólica y cardiovascular de la mujer.</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Dificultad para conciliar el sueño, permanecer dormido o lograr un descanso reparador, afectando el bienestar físico, mental y emocional.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Etapa de transición hormonal caracterizada por la disminución progresiva de estrógenos, que puede afectar la salud física, emocional, metabólica, ósea, urinaria y sexual de la mujer.</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Alteraciones de la próstata que pueden afectar la micción, producir inflamación o molestias y, en algunos casos, asociarse con cambios en la función sexual.</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>PAT_00103</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Perimenopausia / Menopausia</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Causas_Patologia</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Factores como Disminución fisiológica de estrógenos y progesterona; envejecimiento ovárico; factores genéticos; hábitos de vida; obesidad; estrés. pueden estar relacionados con cuál de las siguientes patologías?</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Quistes ováricos funcionales</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Apoyo a la salud reproductiva femenina y planificación del embarazo</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Caída de cabello (Alopecia)</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Perimenopausia / Menopausia</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>PAT_00104</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Perimenopausia / Menopausia</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Sintomas_Patologia</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Una persona presenta señales como Alteraciones menstruales; sofocos; sudoración nocturna; cambios del estado de ánimo; insomnio; disminución de la libido; resequedad vaginal; aumento de peso; caída del cabello; cambios en la piel; dolor articular; fatiga; infecciones urinarias recurrentes.. ¿Con cuál de las siguientes patologías se relacionan?</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Perimenopausia / Menopausia</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Artritis inflamatoria</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Quistes ováricos funcionales</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Vitalidad masculina y apoyo hormonal (Hipogonadismo / Deficiencia de testosterona*)</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>PAT_00105</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Insomnio</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Patologia_Descripcion</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>¿Cuál de las siguientes descripciones corresponde a Insomnio?</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Dificultad para conciliar el sueño, permanecer dormido o lograr un descanso reparador, afectando el bienestar físico, mental y emocional.</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Dolor localizado en la zona lumbar que puede relacionarse con músculos, columna o irritación del nervio ciático, pudiendo extenderse hacia glúteo o pierna.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Trastorno hormonal y metabólico caracterizado por alteraciones en la ovulación, exceso de andrógenos y, con frecuencia, resistencia a la insulina, que puede afectar la salud reproductiva, metabólica y cardiovascular de la mujer.</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Pérdida de densidad o volumen del cabello; puede ser temporal o progresiva según la causa.</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>PAT_00106</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Insomnio</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Causas_Patologia</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Factores como Estrés; ansiedad; exceso de cortisol; cambios hormonales (perimenopausia/menopausia); malos hábitos de sueño; uso de pantallas antes de dormir; consumo excesivo de cafeína, alcohol o nicotina; dolor crónico; algunos medicamentos; trastornos emocionales; deficiencia de magnesio. pueden estar relacionados con cuál de las siguientes patologías?</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Insomnio</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Espolón calcáneo / dolor de talón (fascitis plantar asociada)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Artrosis (desgaste articular / osteoartritis)</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Salud prostática / Molestias prostáticas</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>PAT_00107</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Insomnio</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Descripcion_Patologia</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Una persona presenta la siguiente descripción: Dificultad para conciliar el sueño, permanecer dormido o lograr un descanso reparador, afectando el bienestar físico, mental y emocional. ¿A cuál de las siguientes patologías corresponde?</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Osteoporosis</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Dolor muscular, contracturas y molestias musculoesqueléticas localizadas</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Salud prostática / Molestias prostáticas</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Insomnio</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>PAT_00108</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Insomnio</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Sintomas_Patologia</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Una persona presenta señales como Dificultad para conciliar el sueño; despertares frecuentes; despertar muy temprano; sensación de sueño poco reparador; cansancio al despertar; somnolencia diurna; irritabilidad; dificultad para concentrarse; disminución del rendimiento físico o mental; fatiga.. ¿Con cuál de las siguientes patologías se relacionan?</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Perimenopausia / Menopausia</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Insomnio</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Control glucémico (Diabetes mellitus tipo 2 / Prediabetes)</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Artritis inflamatoria</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>PAT_00109</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Varicocele (Apoyo a la salud vascular y reproductiva masculina)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Descripcion_Patologia</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Una persona presenta la siguiente descripción: Dilatación anormal de las venas del cordón espermático, generalmente en el lado izquierdo, que puede afectar la circulación testicular y, en algunos casos, la fertilidad, la producción de testosterona o generar molestias locales. ¿A cuál de las siguientes patologías corresponde?</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Varicocele (Apoyo a la salud vascular y reproductiva masculina)</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Osteoporosis</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Perimenopausia / Menopausia</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Artrosis (desgaste articular / osteoartritis)</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>P008</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>PAT_00110</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Varicocele (Apoyo a la salud vascular y reproductiva masculina)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Sintomas_Patologia</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Una persona presenta señales como Diagnóstico médico de varicocele; sensación de pesadez o dolor en el escroto; molestias que aumentan al estar de pie o al realizar esfuerzo; disminución de la fertilidad; disminución de la vitalidad masculina; reducción de las erecciones matutinas; disminución de la libido (en algunos casos).. ¿Con cuál de las siguientes patologías se relacionan?</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Caída de cabello (Alopecia)</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Osteoporosis</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Apoyo a la salud reproductiva femenina y planificación del embarazo</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Varicocele (Apoyo a la salud vascular y reproductiva masculina)</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>P008</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>PAT_00111</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Varicocele (Apoyo a la salud vascular y reproductiva masculina)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Patologia_Descripcion</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>¿Cuál de las siguientes descripciones corresponde a Varicocele (Apoyo a la salud vascular y reproductiva masculina)?</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Dolor localizado en la zona lumbar que puede relacionarse con músculos, columna o irritación del nervio ciático, pudiendo extenderse hacia glúteo o pierna.</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Disminución de la energía, la fuerza, el deseo sexual o el rendimiento físico que puede estar relacionada con la edad, el estilo de vida, deficiencias nutricionales o alteraciones hormonales.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Etapa de transición hormonal caracterizada por la disminución progresiva de estrógenos, que puede afectar la salud física, emocional, metabólica, ósea, urinaria y sexual de la mujer.</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Dilatación anormal de las venas del cordón espermático, generalmente en el lado izquierdo, que puede afectar la circulación testicular y, en algunos casos, la fertilidad, la producción de testosterona o generar molestias locales.</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>P008</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>PAT_00112</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Varicocele (Apoyo a la salud vascular y reproductiva masculina)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Causas_Patologia</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Factores como Insuficiencia de las válvulas venosas del cordón espermático; predisposición anatómica; aumento de la presión venosa; permanecer largos períodos de pie; esfuerzo físico intenso; factores hereditarios. pueden estar relacionados con cuál de las siguientes patologías?</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Ciática / Lumbalgia</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Fibromialgia</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Espolón calcáneo / dolor de talón (fascitis plantar asociada)</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Varicocele (Apoyo a la salud vascular y reproductiva masculina)</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>P008</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>PAT_00113</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Bienestar íntimo femenino y función sexual</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Causas_Patologia</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Factores como Disminución de estrógenos (perimenopausia/menopausia); estrés o ansiedad; alteraciones de la circulación; resequedad vaginal; alteración de la microbiota vaginal; diabetes; algunos medicamentos; enfermedades crónicas; fatiga o alteraciones del sueño. pueden estar relacionados con cuál de las siguientes patologías?</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Fibromialgia</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Varicocele (Apoyo a la salud vascular y reproductiva masculina)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Síndrome de Ovario Poliquístico (SOP)</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Bienestar íntimo femenino y función sexual</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>P009</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>PAT_00114</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Bienestar íntimo femenino y función sexual</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Sintomas_Patologia</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Una persona presenta señales como Disminución de la libido; resequedad vaginal; disminución de la lubricación; molestias o dolor durante las relaciones sexuales; menor sensibilidad o excitación; dificultad para alcanzar el orgasmo; infecciones urinarias o vaginales recurrentes; disminución del bienestar íntimo.. ¿Con cuál de las siguientes patologías se relacionan?</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Vitalidad masculina y apoyo hormonal (Hipogonadismo / Deficiencia de testosterona*)</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Espolón calcáneo / dolor de talón (fascitis plantar asociada)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Síndrome de Ovario Poliquístico (SOP)</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Bienestar íntimo femenino y función sexual</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>P009</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>PAT_00115</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Bienestar íntimo femenino y función sexual</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Descripcion_Patologia</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Una persona presenta la siguiente descripción: Disminución del deseo sexual o alteraciones del bienestar íntimo que pueden afectar la satisfacción durante las relaciones sexuales. Puede estar relacionada con factores hormonales, emocionales, circulatorios, metabólicos o alteraciones de la flora vaginal. ¿A cuál de las siguientes patologías corresponde?</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Bienestar íntimo femenino y función sexual</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Control glucémico (Diabetes mellitus tipo 2 / Prediabetes)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Perimenopausia / Menopausia</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Caída de cabello (Alopecia)</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>P009</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>PAT_00116</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Bienestar íntimo femenino y función sexual</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Patologia_Descripcion</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>¿Cuál de las siguientes descripciones corresponde a Bienestar íntimo femenino y función sexual?</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Disminución del deseo sexual o alteraciones del bienestar íntimo que pueden afectar la satisfacción durante las relaciones sexuales. Puede estar relacionada con factores hormonales, emocionales, circulatorios, metabólicos o alteraciones de la flora vaginal.</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Dificultad para conciliar el sueño, permanecer dormido o lograr un descanso reparador, afectando el bienestar físico, mental y emocional.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Molestia localizada en la zona del talón que suele relacionarse con irritación de tejidos de soporte del pie y puede generar dolor al caminar o permanecer de pie.</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Condición en la que uno o varios factores nutricionales, hormonales, metabólicos, emocionales o de estilo de vida pueden disminuir las condiciones óptimas para la concepción. El sistema brinda apoyo nutricional y bienestar reproductivo como complemento y no reemplaza la valoración médica especializada.</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>P009</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>PAT_00117</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Apoyo a la salud reproductiva femenina y planificación del embarazo</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Patologia_Descripcion</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>¿Cuál de las siguientes descripciones corresponde a Apoyo a la salud reproductiva femenina y planificación del embarazo?</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Disminución del deseo sexual o alteraciones del bienestar íntimo que pueden afectar la satisfacción durante las relaciones sexuales. Puede estar relacionada con factores hormonales, emocionales, circulatorios, metabólicos o alteraciones de la flora vaginal.</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Condición en la que uno o varios factores nutricionales, hormonales, metabólicos, emocionales o de estilo de vida pueden disminuir las condiciones óptimas para la concepción. El sistema brinda apoyo nutricional y bienestar reproductivo como complemento y no reemplaza la valoración médica especializada.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Disminución de la energía, la fuerza, el deseo sexual o el rendimiento físico que puede estar relacionada con la edad, el estilo de vida, deficiencias nutricionales o alteraciones hormonales.</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Enfermedad inflamatoria crónica en la que tejido similar al endometrio crece fuera del útero, ocasionando dolor pélvico, inflamación y, en algunas mujeres, dificultades para lograr el embarazo.</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>P010</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>PAT_00118</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Apoyo a la salud reproductiva femenina y planificación del embarazo</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Sintomas_Patologia</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Una persona presenta señales como Dificultad para lograr embarazo; planificación del embarazo; ciclos menstruales irregulares; antecedentes de infertilidad; fatiga o deficiencias nutricionales; diagnóstico de baja reserva ovárica o alteraciones ovulatorias; antecedentes de aborto temprano; deseo de optimizar el estado nutricional antes de la concepción.. ¿Con cuál de las siguientes patologías se relacionan?</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Ciática / Lumbalgia</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Perimenopausia / Menopausia</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Artritis inflamatoria</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Apoyo a la salud reproductiva femenina y planificación del embarazo</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>P010</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>PAT_00119</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Apoyo a la salud reproductiva femenina y planificación del embarazo</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Causas_Patologia</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Factores como Déficit nutricional (ácido fólico, hierro, zinc, vitamina D); estrés crónico; disminución del flujo sanguíneo uterino; resistencia a la insulina o síndrome de ovario poliquístico; sobrepeso u obesidad; edad materna avanzada; hábitos de vida poco saludables; enfermedades ginecológicas o endocrinas. pueden estar relacionados con cuál de las siguientes patologías?</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Quistes ováricos funcionales</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Osteoporosis</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Apoyo a la salud reproductiva femenina y planificación del embarazo</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Ciática / Lumbalgia</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>P010</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>PAT_00120</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Apoyo a la salud reproductiva femenina y planificación del embarazo</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Descripcion_Patologia</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Una persona presenta la siguiente descripción: Condición en la que uno o varios factores nutricionales, hormonales, metabólicos, emocionales o de estilo de vida pueden disminuir las condiciones óptimas para la concepción. El sistema brinda apoyo nutricional y bienestar reproductivo como complemento y no reemplaza la valoración médica especializada. ¿A cuál de las siguientes patologías corresponde?</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Control glucémico (Diabetes mellitus tipo 2 / Prediabetes)</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Apoyo a la salud reproductiva femenina y planificación del embarazo</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Insomnio</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Bienestar íntimo femenino y función sexual</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>P010</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>PAT_00121</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Síndrome de Ovario Poliquístico (SOP)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Causas_Patologia</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Factores como Predisposición genética; resistencia a la insulina; sobrepeso u obesidad; alteraciones hormonales; inflamación crónica de bajo grado; sedentarismo; factores ambientales. pueden estar relacionados con cuál de las siguientes patologías?</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Salud prostática / Molestias prostáticas</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Síndrome de Ovario Poliquístico (SOP)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Bienestar íntimo femenino y función sexual</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Ciática / Lumbalgia</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>PAT_00122</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Síndrome de Ovario Poliquístico (SOP)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Sintomas_Patologia</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Una persona presenta señales como Menstruaciones irregulares o ausencia de menstruación; dificultad para quedar embarazada; acné; exceso de vello corporal o facial; caída del cabello; aumento de peso; resistencia a la insulina; ovarios con múltiples folículos en ecografía.. ¿Con cuál de las siguientes patologías se relacionan?</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Síndrome de Ovario Poliquístico (SOP)</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Varicocele (Apoyo a la salud vascular y reproductiva masculina)</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Dolor muscular, contracturas y molestias musculoesqueléticas localizadas</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Fibromialgia</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>PAT_00123</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Síndrome de Ovario Poliquístico (SOP)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Patologia_Descripcion</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>¿Cuál de las siguientes descripciones corresponde a Síndrome de Ovario Poliquístico (SOP)?</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Disminución de la energía, la fuerza, el deseo sexual o el rendimiento físico que puede estar relacionada con la edad, el estilo de vida, deficiencias nutricionales o alteraciones hormonales.</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Molestias relacionadas con tensión, sobrecarga o irritación de músculos y tejidos blandos, que pueden afectar cuello, espalda u otras zonas del cuerpo.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Trastorno hormonal y metabólico caracterizado por alteraciones en la ovulación, exceso de andrógenos y, con frecuencia, resistencia a la insulina, que puede afectar la salud reproductiva, metabólica y cardiovascular de la mujer.</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Condición en la que existe inflamación dentro de una o varias articulaciones, causando dolor, rigidez y sensibilidad. Algunas formas pueden tener origen autoinmune y requieren seguimiento médico.</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>PAT_00124</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Síndrome de Ovario Poliquístico (SOP)</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Descripcion_Patologia</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Una persona presenta la siguiente descripción: Trastorno hormonal y metabólico caracterizado por alteraciones en la ovulación, exceso de andrógenos y, con frecuencia, resistencia a la insulina, que puede afectar la salud reproductiva, metabólica y cardiovascular de la mujer. ¿A cuál de las siguientes patologías corresponde?</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Ciática / Lumbalgia</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Perimenopausia / Menopausia</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Síndrome de Ovario Poliquístico (SOP)</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Artrosis (desgaste articular / osteoartritis)</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>PAT_00125</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Quistes ováricos funcionales</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Sintomas_Patologia</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Una persona presenta señales como Dolor pélvico unilateral; sensación de presión o pesadez en la pelvis; dolor durante las relaciones sexuales; alteraciones del ciclo menstrual; distensión abdominal; en muchos casos ausencia de síntomas.. ¿Con cuál de las siguientes patologías se relacionan?</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Quistes ováricos funcionales</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Artritis inflamatoria</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Dolor muscular, contracturas y molestias musculoesqueléticas localizadas</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Varicocele (Apoyo a la salud vascular y reproductiva masculina)</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>PAT_00126</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Quistes ováricos funcionales</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Patologia_Descripcion</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>¿Cuál de las siguientes descripciones corresponde a Quistes ováricos funcionales?</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Dolor localizado en la zona lumbar que puede relacionarse con músculos, columna o irritación del nervio ciático, pudiendo extenderse hacia glúteo o pierna.</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Alteración del metabolismo de la glucosa que ocasiona niveles elevados de azúcar en sangre o dificultad para mantenerlos dentro de rangos normales.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Presencia de quistes benignos que se forman durante el ciclo menstrual y que, en la mayoría de los casos, desaparecen espontáneamente, aunque algunos pueden producir dolor o alteraciones menstruales.</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Dilatación anormal de las venas del cordón espermático, generalmente en el lado izquierdo, que puede afectar la circulación testicular y, en algunos casos, la fertilidad, la producción de testosterona o generar molestias locales.</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>PAT_00127</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Quistes ováricos funcionales</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Descripcion_Patologia</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Una persona presenta la siguiente descripción: Presencia de quistes benignos que se forman durante el ciclo menstrual y que, en la mayoría de los casos, desaparecen espontáneamente, aunque algunos pueden producir dolor o alteraciones menstruales. ¿A cuál de las siguientes patologías corresponde?</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Caída de cabello (Alopecia)</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Quistes ováricos funcionales</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Endometriosis</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Disfunción sexual masculina / Dificultad para la erección</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>PAT_00128</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Quistes ováricos funcionales</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Causas_Patologia</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Factores como Cambios normales del ciclo ovulatorio; alteraciones hormonales; algunos tratamientos de fertilidad; antecedentes de quistes ováricos. pueden estar relacionados con cuál de las siguientes patologías?</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Apoyo a la salud reproductiva femenina y planificación del embarazo</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Perimenopausia / Menopausia</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Quistes ováricos funcionales</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Espolón calcáneo / dolor de talón (fascitis plantar asociada)</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>PAT_00129</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Endometriosis</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Patologia_Descripcion</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>¿Cuál de las siguientes descripciones corresponde a Endometriosis?</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Enfermedad en la que los huesos pierden densidad y resistencia, aumentando el riesgo de fracturas, especialmente en columna, cadera y muñeca. Puede avanzar silenciosamente durante años sin síntomas evidentes.</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Dificultad para conciliar el sueño, permanecer dormido o lograr un descanso reparador, afectando el bienestar físico, mental y emocional.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Dolor localizado en la zona lumbar que puede relacionarse con músculos, columna o irritación del nervio ciático, pudiendo extenderse hacia glúteo o pierna.</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Enfermedad inflamatoria crónica en la que tejido similar al endometrio crece fuera del útero, ocasionando dolor pélvico, inflamación y, en algunas mujeres, dificultades para lograr el embarazo.</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>P013</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>PAT_00130</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Endometriosis</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Causas_Patologia</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Factores como Predisposición genética; menstruación retrógrada; alteraciones inmunológicas; factores hormonales; inflamación crónica. pueden estar relacionados con cuál de las siguientes patologías?</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Osteoporosis</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Salud prostática / Molestias prostáticas</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Endometriosis</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Caída de cabello (Alopecia)</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>P013</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>PAT_00131</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Endometriosis</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Descripcion_Patologia</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Una persona presenta la siguiente descripción: Enfermedad inflamatoria crónica en la que tejido similar al endometrio crece fuera del útero, ocasionando dolor pélvico, inflamación y, en algunas mujeres, dificultades para lograr el embarazo. ¿A cuál de las siguientes patologías corresponde?</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Vitalidad masculina y apoyo hormonal (Hipogonadismo / Deficiencia de testosterona*)</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Endometriosis</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Bienestar íntimo femenino y función sexual</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Espolón calcáneo / dolor de talón (fascitis plantar asociada)</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>P013</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>PAT_00132</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Endometriosis</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Sintomas_Patologia</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Una persona presenta señales como Dolor menstrual intenso; dolor pélvico crónico; dolor durante las relaciones sexuales; sangrado menstrual abundante o prolongado; dolor al evacuar o al orinar durante la menstruación; infertilidad; fatiga.. ¿Con cuál de las siguientes patologías se relacionan?</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Varicocele (Apoyo a la salud vascular y reproductiva masculina)</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Disfunción sexual masculina / Dificultad para la erección</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Ciática / Lumbalgia</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Endometriosis</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>P013</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>PAT_00133</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Osteoporosis</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Sintomas_Patologia</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Una persona presenta señales como Dolor de espalda frecuente; pérdida de estatura con los años; postura encorvada; fracturas ante golpes leves; debilidad muscular; disminución de fuerza; dificultad para mantener actividad física; antecedentes familiares de osteoporosis; menopausia o edad avanzada.. ¿Con cuál de las siguientes patologías se relacionan?</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Osteoporosis</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Insomnio</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Artritis inflamatoria</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Salud prostática / Molestias prostáticas</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>P014</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>PAT_00134</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Osteoporosis</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Causas_Patologia</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Factores como Envejecimiento; menopausia y disminución de estrógenos; bajo consumo de calcio y vitamina D; poca exposición solar; sedentarismo; bajo peso corporal; antecedentes familiares; tabaquismo/alcohol; uso prolongado de corticoides; alteraciones hormonales (tiroides/paratiroides). pueden estar relacionados con cuál de las siguientes patologías?</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Osteoporosis</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Síndrome de Ovario Poliquístico (SOP)</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Varicocele (Apoyo a la salud vascular y reproductiva masculina)</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Vitalidad masculina y apoyo hormonal (Hipogonadismo / Deficiencia de testosterona*)</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>P014</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>PAT_00135</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Osteoporosis</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Patologia_Descripcion</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>¿Cuál de las siguientes descripciones corresponde a Osteoporosis?</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Trastorno hormonal y metabólico caracterizado por alteraciones en la ovulación, exceso de andrógenos y, con frecuencia, resistencia a la insulina, que puede afectar la salud reproductiva, metabólica y cardiovascular de la mujer.</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Enfermedad degenerativa de las articulaciones en la que el cartílago que protege los huesos se deteriora progresivamente, generando dolor, rigidez y pérdida de movilidad.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Enfermedad en la que los huesos pierden densidad y resistencia, aumentando el riesgo de fracturas, especialmente en columna, cadera y muñeca. Puede avanzar silenciosamente durante años sin síntomas evidentes.</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Condición en la que existe inflamación dentro de una o varias articulaciones, causando dolor, rigidez y sensibilidad. Algunas formas pueden tener origen autoinmune y requieren seguimiento médico.</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>P014</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>PAT_00136</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Osteoporosis</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Descripcion_Patologia</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Una persona presenta la siguiente descripción: Enfermedad en la que los huesos pierden densidad y resistencia, aumentando el riesgo de fracturas, especialmente en columna, cadera y muñeca. Puede avanzar silenciosamente durante años sin síntomas evidentes. ¿A cuál de las siguientes patologías corresponde?</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Varicocele (Apoyo a la salud vascular y reproductiva masculina)</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Disfunción sexual masculina / Dificultad para la erección</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Osteoporosis</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Espolón calcáneo / dolor de talón (fascitis plantar asociada)</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>P014</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>PAT_00137</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Artrosis (desgaste articular / osteoartritis)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Causas_Patologia</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Factores como Envejecimiento; desgaste progresivo de la articulación; sobrepeso; lesiones articulares previas; movimientos repetitivos; sobrecarga mecánica; factores hereditarios. pueden estar relacionados con cuál de las siguientes patologías?</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Control glucémico (Diabetes mellitus tipo 2 / Prediabetes)</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Espolón calcáneo / dolor de talón (fascitis plantar asociada)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Insomnio</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Artrosis (desgaste articular / osteoartritis)</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>P015</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>PAT_00138</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Artrosis (desgaste articular / osteoartritis)</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Descripcion_Patologia</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Una persona presenta la siguiente descripción: Enfermedad degenerativa de las articulaciones en la que el cartílago que protege los huesos se deteriora progresivamente, generando dolor, rigidez y pérdida de movilidad. ¿A cuál de las siguientes patologías corresponde?</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Bienestar íntimo femenino y función sexual</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Artrosis (desgaste articular / osteoartritis)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Apoyo a la salud reproductiva femenina y planificación del embarazo</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Disfunción sexual masculina / Dificultad para la erección</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>P015</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>PAT_00139</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Artrosis (desgaste articular / osteoartritis)</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Patologia_Descripcion</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>¿Cuál de las siguientes descripciones corresponde a Artrosis (desgaste articular / osteoartritis)?</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Disminución del deseo sexual o alteraciones del bienestar íntimo que pueden afectar la satisfacción durante las relaciones sexuales. Puede estar relacionada con factores hormonales, emocionales, circulatorios, metabólicos o alteraciones de la flora vaginal.</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Trastorno hormonal y metabólico caracterizado por alteraciones en la ovulación, exceso de andrógenos y, con frecuencia, resistencia a la insulina, que puede afectar la salud reproductiva, metabólica y cardiovascular de la mujer.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Enfermedad degenerativa de las articulaciones en la que el cartílago que protege los huesos se deteriora progresivamente, generando dolor, rigidez y pérdida de movilidad.</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Dificultad persistente para lograr o mantener una erección suficiente para una relación sexual satisfactoria. Puede estar relacionada con factores físicos, hormonales, circulatorios, prostáticos o emocionales.</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>P015</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>PAT_00140</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Artrosis (desgaste articular / osteoartritis)</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Sintomas_Patologia</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Una persona presenta señales como Dolor en rodillas, cadera, manos o columna; rigidez después del reposo; dificultad para movilizar la articulación; crujidos o sensación de roce; disminución de movilidad; molestias que aumentan con el uso de la articulación.. ¿Con cuál de las siguientes patologías se relacionan?</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Espolón calcáneo / dolor de talón (fascitis plantar asociada)</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Artritis inflamatoria</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Salud prostática / Molestias prostáticas</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Artrosis (desgaste articular / osteoartritis)</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>P015</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>PAT_00141</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Artritis inflamatoria</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Sintomas_Patologia</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Una persona presenta señales como Dolor articular; inflamación visible; articulaciones calientes o sensibles; rigidez prolongada especialmente al despertar; dificultad para mover la articulación; fatiga asociada; molestias en varias articulaciones.. ¿Con cuál de las siguientes patologías se relacionan?</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Artritis inflamatoria</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Apoyo a la salud reproductiva femenina y planificación del embarazo</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Insomnio</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Control glucémico (Diabetes mellitus tipo 2 / Prediabetes)</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>P016</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>PAT_00142</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Artritis inflamatoria</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Causas_Patologia</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Factores como Alteraciones del sistema inmunológico; predisposición genética; procesos inflamatorios crónicos; infecciones previas en algunos casos; factores ambientales. pueden estar relacionados con cuál de las siguientes patologías?</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Bienestar íntimo femenino y función sexual</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Dolor muscular, contracturas y molestias musculoesqueléticas localizadas</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Artritis inflamatoria</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Síndrome de Ovario Poliquístico (SOP)</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>P016</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>PAT_00143</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Artritis inflamatoria</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Patologia_Descripcion</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>¿Cuál de las siguientes descripciones corresponde a Artritis inflamatoria?</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Enfermedad en la que los huesos pierden densidad y resistencia, aumentando el riesgo de fracturas, especialmente en columna, cadera y muñeca. Puede avanzar silenciosamente durante años sin síntomas evidentes.</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Condición en la que existe inflamación dentro de una o varias articulaciones, causando dolor, rigidez y sensibilidad. Algunas formas pueden tener origen autoinmune y requieren seguimiento médico.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Dolor localizado en la zona lumbar que puede relacionarse con músculos, columna o irritación del nervio ciático, pudiendo extenderse hacia glúteo o pierna.</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Trastorno hormonal y metabólico caracterizado por alteraciones en la ovulación, exceso de andrógenos y, con frecuencia, resistencia a la insulina, que puede afectar la salud reproductiva, metabólica y cardiovascular de la mujer.</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>P016</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>PAT_00144</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Artritis inflamatoria</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Descripcion_Patologia</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Una persona presenta la siguiente descripción: Condición en la que existe inflamación dentro de una o varias articulaciones, causando dolor, rigidez y sensibilidad. Algunas formas pueden tener origen autoinmune y requieren seguimiento médico. ¿A cuál de las siguientes patologías corresponde?</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Artritis inflamatoria</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Fibromialgia</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Artrosis (desgaste articular / osteoartritis)</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Apoyo a la salud reproductiva femenina y planificación del embarazo</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>P016</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>PAT_00145</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Ciática / Lumbalgia</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Patologia_Descripcion</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>¿Cuál de las siguientes descripciones corresponde a Ciática / Lumbalgia?</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Enfermedad degenerativa de las articulaciones en la que el cartílago que protege los huesos se deteriora progresivamente, generando dolor, rigidez y pérdida de movilidad.</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Dolor localizado en la zona lumbar que puede relacionarse con músculos, columna o irritación del nervio ciático, pudiendo extenderse hacia glúteo o pierna.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Condición en la que uno o varios factores nutricionales, hormonales, metabólicos, emocionales o de estilo de vida pueden disminuir las condiciones óptimas para la concepción. El sistema brinda apoyo nutricional y bienestar reproductivo como complemento y no reemplaza la valoración médica especializada.</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Enfermedad en la que los huesos pierden densidad y resistencia, aumentando el riesgo de fracturas, especialmente en columna, cadera y muñeca. Puede avanzar silenciosamente durante años sin síntomas evidentes.</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>P017</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>PAT_00146</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Ciática / Lumbalgia</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Descripcion_Patologia</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Una persona presenta la siguiente descripción: Dolor localizado en la zona lumbar que puede relacionarse con músculos, columna o irritación del nervio ciático, pudiendo extenderse hacia glúteo o pierna. ¿A cuál de las siguientes patologías corresponde?</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Fibromialgia</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Apoyo a la salud reproductiva femenina y planificación del embarazo</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Ciática / Lumbalgia</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Control glucémico (Diabetes mellitus tipo 2 / Prediabetes)</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>P017</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>PAT_00147</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Ciática / Lumbalgia</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Sintomas_Patologia</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Una persona presenta señales como Dolor lumbar; dolor que baja hacia glúteo o pierna; sensación de tirón; rigidez de espalda; dificultad para moverse; molestias después de permanecer mucho tiempo sentado o de pie.. ¿Con cuál de las siguientes patologías se relacionan?</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Disfunción sexual masculina / Dificultad para la erección</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Ciática / Lumbalgia</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Síndrome de Ovario Poliquístico (SOP)</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Bienestar íntimo femenino y función sexual</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>P017</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>PAT_00148</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Ciática / Lumbalgia</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Causas_Patologia</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Factores como Sobrecarga física; malas posturas; esfuerzo repetitivo; alteraciones de columna; tensión muscular; sedentarismo; lesiones. pueden estar relacionados con cuál de las siguientes patologías?</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Bienestar íntimo femenino y función sexual</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Control glucémico (Diabetes mellitus tipo 2 / Prediabetes)</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Espolón calcáneo / dolor de talón (fascitis plantar asociada)</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Ciática / Lumbalgia</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>P017</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>PAT_00149</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Dolor muscular, contracturas y molestias musculoesqueléticas localizadas</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Causas_Patologia</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Factores como Esfuerzo físico; malas posturas; estrés; tensión muscular; ejercicio intenso; movimientos repetitivos; golpes o sobrecarga. pueden estar relacionados con cuál de las siguientes patologías?</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Caída de cabello (Alopecia)</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Dolor muscular, contracturas y molestias musculoesqueléticas localizadas</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Endometriosis</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Vitalidad masculina y apoyo hormonal (Hipogonadismo / Deficiencia de testosterona*)</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>P018</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>PAT_00150</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Dolor muscular, contracturas y molestias musculoesqueléticas localizadas</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Patologia_Descripcion</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>¿Cuál de las siguientes descripciones corresponde a Dolor muscular, contracturas y molestias musculoesqueléticas localizadas?</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Condición en la que existe inflamación dentro de una o varias articulaciones, causando dolor, rigidez y sensibilidad. Algunas formas pueden tener origen autoinmune y requieren seguimiento médico.</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Molestias relacionadas con tensión, sobrecarga o irritación de músculos y tejidos blandos, que pueden afectar cuello, espalda u otras zonas del cuerpo.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Alteración del metabolismo de la glucosa que ocasiona niveles elevados de azúcar en sangre o dificultad para mantenerlos dentro de rangos normales.</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Dificultad para conciliar el sueño, permanecer dormido o lograr un descanso reparador, afectando el bienestar físico, mental y emocional.</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>P018</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>PAT_00151</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Dolor muscular, contracturas y molestias musculoesqueléticas localizadas</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Descripcion_Patologia</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Una persona presenta la siguiente descripción: Molestias relacionadas con tensión, sobrecarga o irritación de músculos y tejidos blandos, que pueden afectar cuello, espalda u otras zonas del cuerpo. ¿A cuál de las siguientes patologías corresponde?</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Salud prostática / Molestias prostáticas</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Dolor muscular, contracturas y molestias musculoesqueléticas localizadas</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Bienestar íntimo femenino y función sexual</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Quistes ováricos funcionales</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>P018</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>PAT_00152</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Dolor muscular, contracturas y molestias musculoesqueléticas localizadas</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Sintomas_Patologia</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Una persona presenta señales como Dolor localizado; sensación de tensión o contractura; rigidez muscular; molestias al mover la zona; cuello o espalda cargados; sensación de cansancio muscular.. ¿Con cuál de las siguientes patologías se relacionan?</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Bienestar íntimo femenino y función sexual</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Síndrome de Ovario Poliquístico (SOP)</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Control glucémico (Diabetes mellitus tipo 2 / Prediabetes)</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Dolor muscular, contracturas y molestias musculoesqueléticas localizadas</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>P018</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>PAT_00153</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Fibromialgia</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Causas_Patologia</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Factores como Alteraciones en la percepción del dolor; factores neurológicos; estrés prolongado; alteraciones del sueño; predisposición individual. pueden estar relacionados con cuál de las siguientes patologías?</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Disfunción sexual masculina / Dificultad para la erección</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Espolón calcáneo / dolor de talón (fascitis plantar asociada)</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Fibromialgia</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Artritis inflamatoria</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>P019</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>PAT_00154</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Fibromialgia</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Descripcion_Patologia</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Una persona presenta la siguiente descripción: Síndrome caracterizado por dolor musculoesquelético generalizado, acompañado frecuentemente de fatiga, alteraciones del sueño y mayor sensibilidad al dolor. ¿A cuál de las siguientes patologías corresponde?</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Fibromialgia</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Bienestar íntimo femenino y función sexual</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Caída de cabello (Alopecia)</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Perimenopausia / Menopausia</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>P019</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>PAT_00155</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Fibromialgia</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Sintomas_Patologia</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Una persona presenta señales como Dolor generalizado en diferentes zonas del cuerpo; cansancio frecuente; sueño no reparador; rigidez; sensibilidad aumentada; dificultad para concentrarse; molestias musculares persistentes.. ¿Con cuál de las siguientes patologías se relacionan?</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Endometriosis</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Fibromialgia</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Bienestar íntimo femenino y función sexual</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Perimenopausia / Menopausia</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>P019</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>PAT_00156</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Fibromialgia</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Patologia_Descripcion</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>¿Cuál de las siguientes descripciones corresponde a Fibromialgia?</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Enfermedad en la que los huesos pierden densidad y resistencia, aumentando el riesgo de fracturas, especialmente en columna, cadera y muñeca. Puede avanzar silenciosamente durante años sin síntomas evidentes.</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Síndrome caracterizado por dolor musculoesquelético generalizado, acompañado frecuentemente de fatiga, alteraciones del sueño y mayor sensibilidad al dolor.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Dilatación anormal de las venas del cordón espermático, generalmente en el lado izquierdo, que puede afectar la circulación testicular y, en algunos casos, la fertilidad, la producción de testosterona o generar molestias locales.</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Condición en la que uno o varios factores nutricionales, hormonales, metabólicos, emocionales o de estilo de vida pueden disminuir las condiciones óptimas para la concepción. El sistema brinda apoyo nutricional y bienestar reproductivo como complemento y no reemplaza la valoración médica especializada.</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>P019</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>PAT_00157</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Espolón calcáneo / dolor de talón (fascitis plantar asociada)</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Descripcion_Patologia</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Una persona presenta la siguiente descripción: Molestia localizada en la zona del talón que suele relacionarse con irritación de tejidos de soporte del pie y puede generar dolor al caminar o permanecer de pie. ¿A cuál de las siguientes patologías corresponde?</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Disfunción sexual masculina / Dificultad para la erección</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Espolón calcáneo / dolor de talón (fascitis plantar asociada)</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Salud prostática / Molestias prostáticas</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Perimenopausia / Menopausia</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>P020</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>PAT_00158</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Espolón calcáneo / dolor de talón (fascitis plantar asociada)</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Causas_Patologia</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Factores como Sobrecarga del pie; aumento de peso; estar mucho tiempo de pie; actividad física intensa; calzado inadecuado; alteraciones de apoyo plantar; envejecimiento. pueden estar relacionados con cuál de las siguientes patologías?</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Espolón calcáneo / dolor de talón (fascitis plantar asociada)</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Endometriosis</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Caída de cabello (Alopecia)</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Insomnio</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>P020</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>PAT_00159</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Espolón calcáneo / dolor de talón (fascitis plantar asociada)</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Sintomas_Patologia</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Una persona presenta señales como Dolor en el talón al dar los primeros pasos; dolor después de periodos de descanso; sensibilidad al apoyar; molestia al caminar; rigidez en la planta del pie.. ¿Con cuál de las siguientes patologías se relacionan?</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Vitalidad masculina y apoyo hormonal (Hipogonadismo / Deficiencia de testosterona*)</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Perimenopausia / Menopausia</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Ciática / Lumbalgia</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Espolón calcáneo / dolor de talón (fascitis plantar asociada)</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>P020</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>PAT_00160</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Patologias</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Espolón calcáneo / dolor de talón (fascitis plantar asociada)</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Patologia_Descripcion</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>¿Cuál de las siguientes descripciones corresponde a Espolón calcáneo / dolor de talón (fascitis plantar asociada)?</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Trastorno hormonal y metabólico caracterizado por alteraciones en la ovulación, exceso de andrógenos y, con frecuencia, resistencia a la insulina, que puede afectar la salud reproductiva, metabólica y cardiovascular de la mujer.</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Enfermedad en la que los huesos pierden densidad y resistencia, aumentando el riesgo de fracturas, especialmente en columna, cadera y muñeca. Puede avanzar silenciosamente durante años sin síntomas evidentes.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Molestia localizada en la zona del talón que suele relacionarse con irritación de tejidos de soporte del pie y puede generar dolor al caminar o permanecer de pie.</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Dificultad persistente para lograr o mantener una erección suficiente para una relación sexual satisfactoria. Puede estar relacionada con factores físicos, hormonales, circulatorios, prostáticos o emocionales.</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:27:54</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>P020</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BANCO_PREGUNTAS_GENERALES.xlsx
+++ b/BANCO_PREGUNTAS_GENERALES.xlsx
@@ -563,7 +563,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -636,7 +636,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -782,7 +782,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M44" t="inlineStr"/>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M54" t="inlineStr"/>
@@ -4432,7 +4432,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
@@ -4724,7 +4724,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
@@ -4797,7 +4797,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M61" t="inlineStr"/>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M65" t="inlineStr"/>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M68" t="inlineStr"/>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
@@ -5527,7 +5527,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
@@ -5673,7 +5673,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
@@ -5965,7 +5965,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
@@ -6403,7 +6403,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
@@ -6622,7 +6622,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
@@ -6987,7 +6987,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
@@ -7279,7 +7279,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
@@ -7352,7 +7352,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
@@ -7425,7 +7425,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
@@ -7936,7 +7936,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
@@ -8155,7 +8155,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
@@ -8228,7 +8228,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
@@ -8447,7 +8447,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
@@ -8593,7 +8593,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M112" t="inlineStr"/>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M113" t="inlineStr"/>
@@ -8739,7 +8739,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
@@ -8812,7 +8812,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
@@ -8958,7 +8958,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
@@ -9031,7 +9031,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
@@ -9177,7 +9177,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M120" t="inlineStr"/>
@@ -9250,7 +9250,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M121" t="inlineStr"/>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M122" t="inlineStr"/>
@@ -9396,7 +9396,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M123" t="inlineStr"/>
@@ -9469,7 +9469,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M124" t="inlineStr"/>
@@ -9542,7 +9542,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M125" t="inlineStr"/>
@@ -9615,7 +9615,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M126" t="inlineStr"/>
@@ -9688,7 +9688,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M127" t="inlineStr"/>
@@ -9761,7 +9761,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M128" t="inlineStr"/>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M129" t="inlineStr"/>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M130" t="inlineStr"/>
@@ -9980,7 +9980,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M131" t="inlineStr"/>
@@ -10053,7 +10053,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M132" t="inlineStr"/>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M133" t="inlineStr"/>
@@ -10199,7 +10199,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M134" t="inlineStr"/>
@@ -10272,7 +10272,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M135" t="inlineStr"/>
@@ -10345,7 +10345,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M136" t="inlineStr"/>
@@ -10418,7 +10418,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M137" t="inlineStr"/>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M138" t="inlineStr"/>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M139" t="inlineStr"/>
@@ -10637,7 +10637,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M140" t="inlineStr"/>
@@ -10710,7 +10710,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M141" t="inlineStr"/>
@@ -10783,7 +10783,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M142" t="inlineStr"/>
@@ -10856,7 +10856,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M143" t="inlineStr"/>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M144" t="inlineStr"/>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M145" t="inlineStr"/>
@@ -11075,7 +11075,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M146" t="inlineStr"/>
@@ -11148,7 +11148,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M147" t="inlineStr"/>
@@ -11221,7 +11221,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M148" t="inlineStr"/>
@@ -11294,7 +11294,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M149" t="inlineStr"/>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M150" t="inlineStr"/>
@@ -11440,7 +11440,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M151" t="inlineStr"/>
@@ -11513,7 +11513,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M152" t="inlineStr"/>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M153" t="inlineStr"/>
@@ -11659,7 +11659,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M154" t="inlineStr"/>
@@ -11732,7 +11732,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M155" t="inlineStr"/>
@@ -11805,7 +11805,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M156" t="inlineStr"/>
@@ -11878,7 +11878,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M157" t="inlineStr"/>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M158" t="inlineStr"/>
@@ -12024,7 +12024,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M159" t="inlineStr"/>
@@ -12097,7 +12097,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M160" t="inlineStr"/>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M161" t="inlineStr"/>

--- a/BANCO_PREGUNTAS_GENERALES.xlsx
+++ b/BANCO_PREGUNTAS_GENERALES.xlsx
@@ -12243,7 +12243,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M162" t="inlineStr"/>
@@ -12316,7 +12316,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M163" t="inlineStr"/>
@@ -12389,7 +12389,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M164" t="inlineStr"/>
@@ -12462,7 +12462,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M165" t="inlineStr"/>
@@ -12535,7 +12535,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M166" t="inlineStr"/>

--- a/BANCO_PREGUNTAS_GENERALES.xlsx
+++ b/BANCO_PREGUNTAS_GENERALES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O166"/>
+  <dimension ref="A1:O171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12550,6 +12550,371 @@
         </is>
       </c>
     </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>RES_00006</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Restricciones</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>FITO OMEGA 3</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Producto_Motivo</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Considere el producto FITO OMEGA 3. Seleccione las DOS afirmaciones que corresponden a información registrada para sus restricciones.</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>El motivo registrado es: Los laxantes estimulantes pueden irritar el colon y agravar estas condiciones..</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>El motivo registrado es: La coenzima Q10 puede interferir con el efecto anticoagulante de algunos medicamentos..</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>El motivo indicado es: Producto de origen marino..</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Otro motivo registrado para este producto es: Puede incrementar el riesgo de sangrado..</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>2026-08-19 00:36:30</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>X007</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>RES_00007</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Restricciones</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>FITO OMEGA 3</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Producto_Motivo</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Considere el producto FITO OMEGA 3. Seleccione las DOS afirmaciones que corresponden a información registrada para sus restricciones.</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>El motivo indicado es: Puede incrementar el riesgo de sangrado..</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Otro motivo registrado para este producto es: Producto de origen marino..</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>El motivo registrado es: La disminución de la función renal puede favorecer la acumulación de magnesio..</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>El motivo registrado es: La suplementación debe individualizarse en personas con alteración renal..</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>2026-08-19 00:36:30</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>X008</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>RES_00008</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Restricciones</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>FITO COLÁGENO MARINO PLUS</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Producto_Motivo</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Considere el producto FITO COLÁGENO MARINO PLUS. Seleccione las DOS afirmaciones que corresponden a información registrada para sus restricciones.</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>El motivo indicado es: Contiene colágeno de origen marino..</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>El motivo registrado es: Puede incrementar el riesgo de sangrado..</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>El motivo registrado es: La L-Arginina favorece la vasodilatación y puede potenciar la disminución de la presión arterial..</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Otro motivo registrado para este producto es: Contiene colágeno de origen marino..</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>2026-08-19 00:36:30</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>X009</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>RES_00009</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Restricciones</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>OSHECAL</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Producto_Motivo</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Considere el producto OSHECAL. Seleccione las DOS afirmaciones que corresponden a información registrada para sus restricciones.</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>El motivo registrado es: La valeriana puede potenciar el efecto sedante de otros medicamentos o sustancias depresoras del sistema nervioso central, aumentando la somnolencia..</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>El motivo registrado es: La vitamina E en dosis suplementarias puede aumentar el riesgo de sangrado en personas con medicamentos que afectan la coagulación..</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Otro motivo registrado para este producto es: La suplementación con calcio debe individualizarse cuando existen alteraciones en eliminación renal o manejo del calcio..</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>El motivo indicado es: Al ser un producto en polvo/multivitamínico puede contener componentes que deben revisarse según la formulación y el control nutricional del usuario..</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>2026-08-19 00:36:30</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>X019</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>RES_00010</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Restricciones</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>OSHECAL</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Producto_Motivo</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Considere el producto OSHECAL. Seleccione las DOS afirmaciones que corresponden a información registrada para sus restricciones.</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>El motivo registrado es: Su aporte elevado de calorías puede favorecer aumento de peso no deseado si no existe demanda energética o entrenamiento..</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>El motivo registrado es: Es un producto orientado al control de peso y no debe utilizarse en personas donde la pérdida de peso no sea apropiada..</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Otro motivo registrado para este producto es: Al ser un producto en polvo/multivitamínico puede contener componentes que deben revisarse según la formulación y el control nutricional del usuario..</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>El motivo indicado es: La suplementación con calcio debe individualizarse cuando existen alteraciones en eliminación renal o manejo del calcio..</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>2026-08-19 00:36:30</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>X020</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BANCO_PREGUNTAS_GENERALES.xlsx
+++ b/BANCO_PREGUNTAS_GENERALES.xlsx
@@ -12608,7 +12608,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M167" t="inlineStr"/>
@@ -12681,7 +12681,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M168" t="inlineStr"/>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADA</t>
         </is>
       </c>
       <c r="M169" t="inlineStr"/>
@@ -12827,7 +12827,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M170" t="inlineStr"/>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADA</t>
         </is>
       </c>
       <c r="M171" t="inlineStr"/>

--- a/BANCO_PREGUNTAS_GENERALES.xlsx
+++ b/BANCO_PREGUNTAS_GENERALES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O171"/>
+  <dimension ref="A1:O176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12915,6 +12915,371 @@
         </is>
       </c>
     </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>RES_00011</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Restricciones</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>CLORURO DE MAGNESIO</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Producto_Restriccion</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>En el producto CLORURO DE MAGNESIO, la situación indicada es: Precaución. ¿Cuál es la característica registrada para esta situación?</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Menores de edad; embarazo; lactancia; obstrucción intestinal; colon irritable activo</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Gastritis erosiva o úlcera péptica activa</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Enfermedad renal conocida o sin evaluación cuando existen factores de riesgo</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Insuficiencia renal moderada o severa; hipermagnesemia diagnosticada.</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>2026-08-19 00:58:22</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>X043</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>RES_00012</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Restricciones</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>FITO VALERIANA</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Producto_Restriccion</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>En el producto FITO VALERIANA, la situación indicada es: Contraindicación / Precaución. ¿Cuál es la característica registrada para esta situación?</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Precaución</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Embarazo; hipertiroidismo no controlado; enfermedades autoinmunes tratadas con inmunomoduladores; uso concomitante de sedantes.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Menores de 12 años; embarazo; lactancia; hipersensibilidad a alguno de sus componentes. Usar con precaución en personas que consumen medicamentos sedantes, ansiolíticos, hipnóticos o alcohol. Evitar conducir u operar maquinaria después de su consumo.</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>Hipercalcemia, enfermedad renal avanzada o antecedentes de alteraciones importantes del metabolismo del calcio</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>2026-08-19 00:58:22</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>X018</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>RES_00013</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Restricciones</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>FITO COLÁGENO MARINO PLUS</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Producto_Restriccion</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>En el producto FITO COLÁGENO MARINO PLUS, la situación indicada es: Contraindicación. ¿Cuál es la característica registrada para esta situación?</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Alergia al pescado o mariscos</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Menores de 12 años sin indicación médica; embarazo; lactancia; hipersensibilidad a alguno de sus componentes. Usar con precaución en personas que reciben medicamentos sedantes o que deben realizar actividades que requieran estado de alerta inmediatamente después de su consumo.</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Menores de 12 años; embarazo; lactancia; hipersensibilidad a alguno de sus componentes. Usar con precaución en personas que consumen medicamentos sedantes, ansiolíticos, hipnóticos o alcohol. Evitar conducir u operar maquinaria después de su consumo.</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Uso de anticoagulantes o antiagregantes; cirugía programada; obstrucción o cálculos biliares.</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>2026-08-19 00:58:22</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>X009</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>RES_00014</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Restricciones</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>CLORURO DE MAGNESIO</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Producto_Restriccion_Motivo</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>En relación con el producto CLORURO DE MAGNESIO, considere la situación Precaución. Seleccione las DOS afirmaciones que corresponden a la información registrada.</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>La característica registrada es: Enfermedad renal avanzada.</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>El motivo registrado es: Los ácidos grasos omega 3 pueden aumentar el efecto antiagregante en personas con tratamientos que afectan la coagulación..</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>La característica registrada es: Insuficiencia renal moderada o severa; hipermagnesemia diagnosticada..</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>El motivo registrado es: La disminución de la función renal puede favorecer la acumulación de magnesio..</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>2026-08-19 00:58:22</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>X043</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>RES_00015</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Restricciones</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>FITO VALERIANA</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Producto_Restriccion_Motivo</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>En relación con el producto FITO VALERIANA, considere la situación Contraindicación / Precaución. Seleccione las DOS afirmaciones que corresponden a la información registrada.</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>El motivo registrado es: Su efecto purgante puede agravar estas condiciones..</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>La característica registrada es: Uso de anticoagulantes, antiagregantes o cirugía próxima.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>La característica registrada es: Menores de 12 años; embarazo; lactancia; hipersensibilidad a alguno de sus componentes. Usar con precaución en personas que consumen medicamentos sedantes, ansiolíticos, hipnóticos o alcohol. Evitar conducir u operar maquinaria después de su consumo..</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>El motivo registrado es: La valeriana puede potenciar el efecto sedante de otros medicamentos o sustancias depresoras del sistema nervioso central, aumentando la somnolencia..</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>2026-08-19 00:58:22</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>X018</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BANCO_PREGUNTAS_GENERALES.xlsx
+++ b/BANCO_PREGUNTAS_GENERALES.xlsx
@@ -12973,7 +12973,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADA</t>
         </is>
       </c>
       <c r="M172" t="inlineStr"/>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M173" t="inlineStr"/>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M174" t="inlineStr"/>

--- a/BANCO_PREGUNTAS_GENERALES.xlsx
+++ b/BANCO_PREGUNTAS_GENERALES.xlsx
@@ -13192,7 +13192,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADA</t>
         </is>
       </c>
       <c r="M175" t="inlineStr"/>
@@ -13265,7 +13265,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>APROBADA</t>
         </is>
       </c>
       <c r="M176" t="inlineStr"/>

--- a/BANCO_PREGUNTAS_GENERALES.xlsx
+++ b/BANCO_PREGUNTAS_GENERALES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O176"/>
+  <dimension ref="A1:O181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13280,6 +13280,371 @@
         </is>
       </c>
     </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>PROD_00001</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Productos</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>OREGANO OIL x 150 SOFTGELS</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Producto_AccionGeneral</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Considere el producto OREGANO OIL x 150 SOFTGELS. ¿Cuál de las siguientes acciones generales corresponde a este producto según la matriz?</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>MODO DE ACCIÓN: acción antifúngica y antibacteriana potente al alterar membrana celular de hongos y bacterias</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Artrifit (dolor reumático)</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Gel de Caléndula (apoyo tópico en piel irritada)</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Apoyo en regulación emocional en personas hipersensibles</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>RECHAZADA</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>2026-08-19 20:26:46</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>oregano oil x 150 softgels||modo de acción: acción antifúngica y antibacteriana potente al alterar membrana celular de hongos y bacterias</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>PROD_00002</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Productos</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>FITO GEL DE CALENDULA x 300 GR</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Producto_AccionGeneral</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Considere el producto FITO GEL DE CALENDULA x 300 GR. ¿Cuál de las siguientes acciones generales corresponde a este producto según la matriz?</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Apoyo en expulsión de flema ligera</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>flor de jamaica con apoyo diurético suave y antioxidante, útil en retención de líquidos. Puede apoyar digestión y sensación de pesadez. COMBINACIONES: Dunplus (pérdida de peso/metabolismo)</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>yantén como calmante tradicional. Gel frío con efecto refrescante que disminuye sensación de ardor e inflamación. Apoyo en regeneración cutánea en quemaduras leves y lesiones superficiales (coadyuvante). COMBINACIONES: Castaño de Indias cápsulas (circulación interna + externa)</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Cloruro de Magnesio (apoyo muscular)</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>RECHAZADA</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>2026-08-19 20:26:46</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>fito gel de calendula x 300 gr||yantén como calmante tradicional. gel frío con efecto refrescante que disminuye sensación de ardor e inflamación. apoyo en regeneración cutánea en quemaduras leves y lesiones superficiales (coadyuvante). combinaciones: castaño de indias cápsulas (circulación interna + externa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>PROD_00003</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Productos</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>FITO ARTRIFIT x 60 CAP</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Producto_AccionGeneral</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Considere el producto FITO ARTRIFIT x 60 CAP. ¿Cuál de las siguientes acciones generales corresponde a este producto según la matriz?</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Magnesio (sistema nervioso)</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Mejora rigidez y movilidad</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Zinc adicional (defensas). FRASE DE VENTA: 'Ayuda a descongestionar y reforzar defensas en gripa con mocos.'</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>apoyo en oxigenación cerebral</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>RECHAZADA</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>2026-08-19 20:26:46</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>fito artrifit x 60 cap||mejora rigidez y movilidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>PROD_00004</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Productos</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>FITO OMEGA 3 x 100 PERLAS</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Producto_AccionGeneral</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Considere el producto FITO OMEGA 3 x 100 PERLAS. ¿Cuál de las siguientes acciones generales corresponde a este producto según la matriz?</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>apoyo antioxidante</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Biotina (cabello si hay déficit). FRASE DE VENTA: 'Detox verde completo: limpia, nutre, energiza y fortalece defensas.'</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Vitamina E cosmética (piel seca). FRASE DE VENTA: 'Calma y regenera tu piel de forma natural.'</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Colágeno Marino (articulaciones/piel)</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>RECHAZADA</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>2026-08-19 20:26:46</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>fito omega 3 x 100 perlas||colágeno marino (articulaciones/piel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>PROD_00005</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Productos</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>FITO GINKGO BILOBA x 100 CAP</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Producto_AccionGeneral</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Considere el producto FITO GINKGO BILOBA x 100 CAP. ¿Cuál de las siguientes acciones generales corresponde a este producto según la matriz?</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>apoyo indirecto en dolor articular leve asociado a componente circulatorio. COMBINACIONES: Breinap (memoria + energía mental)</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Nutrición de fibra capilar y piel</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>apoyo en piel (regulación de inflamación y sebo, acné)</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Apoyo en conciliación del sueño cuando hay nerviosismo</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>RECHAZADA</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>2026-08-19 20:26:46</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>fito ginkgo biloba x 100 cap||apoyo indirecto en dolor articular leve asociado a componente circulatorio. combinaciones: breinap (memoria + energía mental)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BANCO_PREGUNTAS_GENERALES.xlsx
+++ b/BANCO_PREGUNTAS_GENERALES.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Banco_General" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Banco" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O181"/>
+  <dimension ref="A1:O183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13645,6 +13645,152 @@
         </is>
       </c>
     </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>PTAG-000002</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Acción General</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Producto-Acción General</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>¿Cuáles de las siguientes acciones generales corresponden al producto FITO CALENDULA FITO X 100 CAP? Seleccione las dos opciones correctas.</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Hidratación profunda</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>perimenopausia/menopausia y defensas bajas</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Apoyo en inflamación de mucosa oral (encías)</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Apoyo en procesos inflamatorios de piel (coadyuvante)</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>3;4</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>APROBADA</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>2026-08-22 19:23:46</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>PTAG-F000036;PTAG-F000394;PTAG-F000121;PTAG-F000120</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>PTAG-000002</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Acción General</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Producto-Acción General</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>¿Cuáles de las siguientes acciones generales corresponden al producto FITO GINKGO BILOBA x 100 CAP? Seleccione las dos opciones correctas.</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Apoyo en adaptación a cambios que alteran el descanso</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>miel con efecto emoliente y calmante de mucosa</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>MODO DE ACCIÓN: mejora microcirculación cerebral y periférica</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>acción antioxidante vascular (flavonoides)</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>3;4</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>RECHAZADA</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>2026-08-22 19:23:46</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>PTAG-F000214;PTAG-F000363;PTAG-F000282;PTAG-F000283</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BANCO_PREGUNTAS_GENERALES.xlsx
+++ b/BANCO_PREGUNTAS_GENERALES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O183"/>
+  <dimension ref="A1:O185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13791,6 +13791,152 @@
         </is>
       </c>
     </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>PTCA-000001</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Componente - Acción</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Producto-Componente-Acción</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>En el producto FITO ACEITE ARGAN MASAJES x 240 ML, ¿cuál de las siguientes acciones corresponde específicamente al componente Aceite de argán?</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Estimula respuesta inmunológica</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>disminuye hiperalerta y tensión, facilitando conciliación del sueño y reduciendo ansiedad. Útil en insomnio por estrés, irritabilidad y síntomas somáticos de ansiedad (tensión, palpitaciones, colon irritable).</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Acción antiinflamatoria tópica</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>Hidratación profunda</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>APROBADA</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>2026-08-22 19:59:11</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>PTCA-F000101;PTCA-F000182;PTCA-F000071;PTCA-F000015</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>PTCA-000001</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Componente - Acción</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Producto-Componente-Acción</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>En el producto FITO ACEITE DE COCO MASAJES X 240 ML, ¿cuál de las siguientes acciones corresponde específicamente al componente Aceite de coco?</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Restauración de barrera lipídica</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Acción antioxidante</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Apoyo en regulación emocional en personas hipersensibles</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>Apoyo en modulación de respuesta inmune en rinitis y alergias leves (coadyuvante). MODO DE ACCIÓN: apoyo en fagocitosis y actividad de células inmunes.</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>APROBADA</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>2026-08-22 19:59:11</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>PTCA-F000024;PTCA-F000029;PTCA-F000107;PTCA-F000105</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BANCO_PREGUNTAS_GENERALES.xlsx
+++ b/BANCO_PREGUNTAS_GENERALES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O185"/>
+  <dimension ref="A1:O187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13937,6 +13937,152 @@
         </is>
       </c>
     </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>PTCA-000002</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Componente - Acción</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Producto-Componente-Acción</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>En el producto FITO BIOTIN 900 MCG X 60 CAP, ¿cuáles de las siguientes acciones corresponden específicamente al componente Biotina (Vitamina B7)? Seleccione las dos opciones correctas.</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>como antioxidante liposoluble que protege membranas celulares y reduce daño oxidativo</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Soporte estructural del cabello y uñas</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Apoyo en estados carenciales</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>Apoyo en bienestar femenino (cólicos leves)</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>2;3</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>APROBADA</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>2026-08-22 20:09:33</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>PTCA-F000179;PTCA-F000004;PTCA-F000006;PTCA-F000067</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>PTCA-000002</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Componente - Acción</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Producto-Componente-Acción</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>En el producto FITO ARTRIFIT x 60 CAP, ¿cuáles de las siguientes acciones corresponden específicamente al componente Extracto seco de Harpagofito (Harpagophytum procumbens)? Seleccione las dos opciones correctas.</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Apoyo en cabello y uñas por déficit. NOTA: producto dulce</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Beneficios progresivos con uso continuo (2–3 meses)</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>y como cofactores en formación de matriz ósea y tejido conectivo</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>Coadyuvante en enfermedades reumáticas</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>2;4</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>RECHAZADA</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>2026-08-22 20:09:33</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>PTCA-F000121;PTCA-F000048;PTCA-F000162;PTCA-F000047</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BANCO_PREGUNTAS_GENERALES.xlsx
+++ b/BANCO_PREGUNTAS_GENERALES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O187"/>
+  <dimension ref="A1:O190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14083,6 +14083,225 @@
         </is>
       </c>
     </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>PTCP-000001</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Categoría principal</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Producto-Categoría principal</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>¿A qué categoría principal pertenece el producto FITO TRATAMIENTO MAJENDY X 15 GR?</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Digestivo / Microbiota</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Osteomuscular / Magnesio</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Respiratorio / Congestión y flema</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>Cabello</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>APROBADA</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>2026-08-22 20:36:08</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>PTCP-F000020;PTCP-F000028;PTCP-F000043;PTCP-F000007</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>PTCP-000001</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Categoría principal</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Producto-Categoría principal</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>¿A qué categoría principal pertenece el producto FITO CRANBERRY EXTRACT X 60 CAP?</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Dermocosmético / Despigmentante nocturno</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Cabello / Piel</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Urinario / Prevención de cistitis</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>Dolor / Anti-inflamatorio tópico</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>APROBADA</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>2026-08-22 20:36:08</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>PTCP-F000032;PTCP-F000009;PTCP-F000031;PTCP-F000025</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>PTCP-000001</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Categoría principal</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Producto-Categoría principal</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>¿A qué categoría principal pertenece el producto FITO ALCACHOFA x 100 CAP?</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Digestivo / Hepático</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Cabello / Piel</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Piel / Hidratación profunda</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>Respiratorio / Gripe con congestión</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>APROBADA</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>2026-08-22 20:36:08</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>PTCP-F000015;PTCP-F000010;PTCP-F000012;PTCP-F000057</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BANCO_PREGUNTAS_GENERALES.xlsx
+++ b/BANCO_PREGUNTAS_GENERALES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O190"/>
+  <dimension ref="A1:O192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14302,6 +14302,152 @@
         </is>
       </c>
     </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>PTCC-000001</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Categoría principal y complementaria</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Producto-Categoría principal-Categoría complementaria</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>¿Cuáles de las siguientes categorías corresponden al producto FITO PROSTENFIT x 60 CAP? Seleccione las dos opciones correctas.</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Cabello</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Próstata</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Uñas; Piel; Déficit nutricional</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>Cabello; Salud masculina; Disfunción sexual asociada a próstata</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>2;4</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>APROBADA</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:17:37</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>PTCC-F000001;PTCC-F000002</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>PTCC-000001</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Categoría principal y complementaria</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Producto-Categoría principal-Categoría complementaria</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>¿Cuáles de las siguientes categorías corresponden al producto FITO GLOBXAN x 60 CAP? Seleccione las dos opciones correctas.</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Caída por debilidad; Cuero cabelludo; Reparación capilar; Daño químico</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Cabello</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Nutrición / Energía</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>Cabello; Fatiga; Recuperación; Rendimiento físico; Déficit nutricional</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>3;4</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>APROBADA</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:17:37</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>PTCC-F000003;PTCC-F000004</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BANCO_PREGUNTAS_GENERALES.xlsx
+++ b/BANCO_PREGUNTAS_GENERALES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O192"/>
+  <dimension ref="A1:O193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14448,6 +14448,79 @@
         </is>
       </c>
     </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>PTG-DS-000001</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Patología</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Definición</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Patología-Definición</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>¿Cuál de las siguientes opciones describe correctamente la patología Artritis inflamatoria?</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Dilatación anormal de las venas del cordón espermático, generalmente en el lado izquierdo, que puede afectar la circulación testicular y, en algunos casos, la fertilidad, la producción de testosterona o generar molestias locales.</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Alteración del metabolismo de la glucosa que ocasiona niveles elevados de azúcar en sangre o dificultad para mantenerlos dentro de rangos normales.</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Condición en la que existe inflamación dentro de una o varias articulaciones, causando dolor, rigidez y sensibilidad. Algunas formas pueden tener origen autoinmune y requieren seguimiento médico.</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>Alteraciones de la próstata que pueden afectar la micción, producir inflamación o molestias y, en algunos casos, asociarse con cambios en la función sexual.</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>APROBADA</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:19:20</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>PTG-F000016</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BANCO_PREGUNTAS_GENERALES.xlsx
+++ b/BANCO_PREGUNTAS_GENERALES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O193"/>
+  <dimension ref="A1:O195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14521,6 +14521,152 @@
         </is>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>PTG-PC-000001</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Patología</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Causas</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Patología-Causas</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>¿Cuál de las siguientes opciones corresponde a las causas frecuentes de la patología Espolón calcáneo / dolor de talón (fascitis plantar asociada)?</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Predisposición genética; resistencia a la insulina; sobrepeso u obesidad; alteraciones hormonales; inflamación crónica de bajo grado; sedentarismo; factores ambientales.</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Sobrecarga del pie; aumento de peso; estar mucho tiempo de pie; actividad física intensa; calzado inadecuado; alteraciones de apoyo plantar; envejecimiento.</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Androgenética (DHT); déficit nutricional (hierro/zinc/biotina/proteína); estrés y alteración del sueño; postparto; perimenopausia/menopausia; cuero cabelludo (caspa/dermatitis); fármacos/quimio; químicos/cosméticos; tiroides.</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>Predisposición genética; menstruación retrógrada; alteraciones inmunológicas; factores hormonales; inflamación crónica.</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>APROBADA</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>2026-08-23 18:01:44</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>PTG-F000020</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>PTG-PC-000001</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Patología</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Causas</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Patología-Causas</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>¿Cuál de las siguientes opciones corresponde a las causas frecuentes de la patología Endometriosis?</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Estrés; ansiedad; exceso de cortisol; cambios hormonales (perimenopausia/menopausia); malos hábitos de sueño; uso de pantallas antes de dormir; consumo excesivo de cafeína, alcohol o nicotina; dolor crónico; algunos medicamentos; trastornos emocionales; deficiencia de magnesio.</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Predisposición genética; menstruación retrógrada; alteraciones inmunológicas; factores hormonales; inflamación crónica.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Androgenética (DHT); déficit nutricional (hierro/zinc/biotina/proteína); estrés y alteración del sueño; postparto; perimenopausia/menopausia; cuero cabelludo (caspa/dermatitis); fármacos/quimio; químicos/cosméticos; tiroides.</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>Resistencia a la insulina; predisposición genética; sobrepeso u obesidad; sedentarismo; alimentación rica en azúcares y carbohidratos refinados; síndrome metabólico; estrés crónico; envejecimiento.</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>APROBADA</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>2026-08-23 18:01:44</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>PTG-F000013</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BANCO_PREGUNTAS_GENERALES.xlsx
+++ b/BANCO_PREGUNTAS_GENERALES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O195"/>
+  <dimension ref="A1:O196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14667,6 +14667,79 @@
         </is>
       </c>
     </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>PTG-ST-000001</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Patología</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Síntomas</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Patología-Síntomas</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>¿Cuáles de las siguientes opciones corresponden a los síntomas o señales clave de la patología Endometriosis?</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Disminución de la libido; dificultad para lograr la erección; dificultad para mantenerla; erecciones menos firmes; disminución del deseo sexual; fatiga.</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Dolor lumbar; dolor que baja hacia glúteo o pierna; sensación de tirón; rigidez de espalda; dificultad para moverse; molestias después de permanecer mucho tiempo sentado o de pie.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Dolor menstrual intenso; dolor pélvico crónico; dolor durante las relaciones sexuales; sangrado menstrual abundante o prolongado; dolor al evacuar o al orinar durante la menstruación; infertilidad; fatiga.</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>Dificultad para conciliar el sueño; despertares frecuentes; despertar muy temprano; sensación de sueño poco reparador; cansancio al despertar; somnolencia diurna; irritabilidad; dificultad para concentrarse; disminución del rendimiento físico o mental; fatiga.</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>APROBADA</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>2026-08-23 18:08:25</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>PTG-F000013</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BANCO_PREGUNTAS_GENERALES.xlsx
+++ b/BANCO_PREGUNTAS_GENERALES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O196"/>
+  <dimension ref="A1:O197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14740,6 +14740,79 @@
         </is>
       </c>
     </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>PTG-PP-000002</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Patología</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Patología-Producto</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>¿Cuál de los siguientes productos está recomendado para la patología Caída de cabello (Alopecia)?</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>FITO MELATONINA</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>FITO SHAMPOO FOLISAN X 400 ML</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>FITO GLOBXAN</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>CURCUMINA</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>APROBADA</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>2026-08-23 18:31:08</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BANCO_PREGUNTAS_GENERALES.xlsx
+++ b/BANCO_PREGUNTAS_GENERALES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O197"/>
+  <dimension ref="A1:O198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14813,6 +14813,79 @@
         </is>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>PTG-PD-000004</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Patología</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Descripción-Producto</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Nivel 2</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Patología-Descripción-Producto</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>¿Cuál de los siguientes productos está recomendado para una patología cuya descripción es la siguiente: Disminución de la energía, la fuerza, el deseo sexual o el rendimiento físico que puede estar relacionada con la edad, el estilo de vida, deficiencias nutricionales o alteraciones hormonales.?</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Derivar al paquete específico de la patología correspondiente (P011 o P005)</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>FITO VINAGRE ZUMO DE MANZANA PREMIUM x 250 ML</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>FITO L-ARGININA + ZINC + MAGNESIO</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>ESENCIA FLORAL PASIFLORA</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>APROBADA</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>2026-08-23 19:40:31</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BANCO_PREGUNTAS_GENERALES.xlsx
+++ b/BANCO_PREGUNTAS_GENERALES.xlsx
@@ -14534,42 +14534,42 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Causas</t>
+          <t>Condición - Producto + Coadyuvantes</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Nivel 1</t>
+          <t>Nivel 2</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Patología-Causas</t>
+          <t>Patología-Condición-Producto-Coadyuvantes</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>¿Cuál de las siguientes opciones corresponde a las causas frecuentes de la patología Espolón calcáneo / dolor de talón (fascitis plantar asociada)?</t>
+          <t>Para la patología Varicocele (Apoyo a la salud vascular y reproductiva masculina), si se presenta el perfil o condición Varicocele sin complicaciones asociadas, ¿cuál sería el paquete recomendado?</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Predisposición genética; resistencia a la insulina; sobrepeso u obesidad; alteraciones hormonales; inflamación crónica de bajo grado; sedentarismo; factores ambientales.</t>
+          <t>INOSITOL (Terceros) | BERBERINA (Terceros); CROMO (Terceros)</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Sobrecarga del pie; aumento de peso; estar mucho tiempo de pie; actividad física intensa; calzado inadecuado; alteraciones de apoyo plantar; envejecimiento.</t>
+          <t>FITO CASTAÑO DE INDIAS | FITO OMEGA 3</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Androgenética (DHT); déficit nutricional (hierro/zinc/biotina/proteína); estrés y alteración del sueño; postparto; perimenopausia/menopausia; cuero cabelludo (caspa/dermatitis); fármacos/quimio; químicos/cosméticos; tiroides.</t>
+          <t>ARTRIFIT | Cloruro de Magnesio; CALGEL</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Predisposición genética; menstruación retrógrada; alteraciones inmunológicas; factores hormonales; inflamación crónica.</t>
+          <t>FITO GLOBXAN | Ninguno</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -14585,12 +14585,12 @@
       <c r="M194" t="inlineStr"/>
       <c r="N194" t="inlineStr">
         <is>
-          <t>2026-08-23 18:01:44</t>
+          <t>2026-08-23 20:13:38</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>PTG-F000020</t>
+          <t>P008</t>
         </is>
       </c>
     </row>

--- a/BANCO_PREGUNTAS_GENERALES.xlsx
+++ b/BANCO_PREGUNTAS_GENERALES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O198"/>
+  <dimension ref="A1:O199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14886,6 +14886,79 @@
         </is>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>PTCOM-000001</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Complementarios</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Producto-Indicaciones-Combinaciones</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>El producto Zarzaparrilla usualmente se recomienda para Acné hormonal; Problemas cutáneos crónicos; Inflamación leve; Retención de líquidos leve; Artritis leve (apoyo). ¿Cuál de las siguientes opciones corresponde a la combinación estratégica recomendada?</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Isowoan; Zinc; L-Arginina; Creatina; Proteína; Ashwagandha</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Alcachofa (detox piel); Orégano (acné inflamatorio); Isowoan (mujer hormonal)</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Proteína; Creatina</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>Fibra; Biotics</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>APROBADA</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:05:42</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>COM-F000002</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BANCO_PREGUNTAS_GENERALES.xlsx
+++ b/BANCO_PREGUNTAS_GENERALES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O199"/>
+  <dimension ref="A1:O200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14959,6 +14959,79 @@
         </is>
       </c>
     </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>PTRX-000001</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Restricciones</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Precaución / Contraindicación</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Producto-Precaución/Contraindicación</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Para el producto CLORURO DE MAGNESIO, ¿cuál de las siguientes corresponde a una precaución o contraindicación para su uso?</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Insuficiencia renal moderada o severa; hipermagnesemia diagnosticada.</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Uso de warfarina u otros anticoagulantes</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Insuficiencia renal moderada o avanzada; hipermagnesemia</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>Persona sedentaria cuyo objetivo es únicamente osteoporosis sin pérdida de masa muscular identificada</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>APROBADA</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:39:44</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>RX-000043</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BANCO_PREGUNTAS_GENERALES.xlsx
+++ b/BANCO_PREGUNTAS_GENERALES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O200"/>
+  <dimension ref="A1:O201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15032,6 +15032,79 @@
         </is>
       </c>
     </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>PTRX-000002</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Restricciones</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Precaución / Contraindicación</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Producto-Precaución/Contraindicación</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Para el producto FITO OMEGA 3, ¿cuál de las siguientes corresponde a una precaución o contraindicación para su uso?</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Uso de anticoagulantes o antiagregantes; cirugía programada; obstrucción o cálculos biliares.</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Embarazo; lactancia; gastritis o úlcera activa; niños pequeños</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Alergia al pescado o mariscos</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>Uso de anticoagulantes, antiagregantes plaquetarios o cirugía próxima</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>APROBADA</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:45:11</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>RX-000007</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BANCO_PREGUNTAS_GENERALES.xlsx
+++ b/BANCO_PREGUNTAS_GENERALES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O201"/>
+  <dimension ref="A1:O202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15105,6 +15105,79 @@
         </is>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>PTRX-000003</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Restricciones</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Precaución / Contraindicación</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Producto-Precaución/Contraindicación</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Para el producto FITO CLORURO DE MAGNESIO, ¿cuál de las siguientes corresponde a una precaución o contraindicación para su uso?</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Enfermedad renal avanzada</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Embarazo; lactancia; antecedentes de herpes recurrente; hipotensión o tratamiento antihipertensivo; insuficiencia renal o hepática avanzada.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Uso concomitante de anticoagulantes o cirugía programada</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>Gastritis erosiva o úlcera péptica activa</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>APROBADA</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>2026-08-24 14:14:34</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>RX-000021</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BANCO_PREGUNTAS_GENERALES.xlsx
+++ b/BANCO_PREGUNTAS_GENERALES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O202"/>
+  <dimension ref="A1:O203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15178,6 +15178,79 @@
         </is>
       </c>
     </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>PTRM-000001</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Restricciones</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Producto / Contraindicación - Motivo</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Producto-Precaución/Contraindicación-Motivo</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>FITO VITAMINA D3 puede generar contraindicaciones asociadas a Hipercalcemia, antecedentes de exceso de vitamina D o enfermedades que alteren metabolismo del calcio debido a que:</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>La suplementación con calcio debe individualizarse cuando existen alteraciones en eliminación renal o manejo del calcio.</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>La vitamina D aumenta la absorción de calcio y debe ajustarse cuando hay alteraciones del metabolismo mineral.</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>El resveratrol puede presentar efecto modulador sobre la agregación plaquetaria y requiere precaución en personas con riesgo de sangrado.</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>La vitamina E en dosis suplementarias puede aumentar el riesgo de sangrado en personas con medicamentos que afectan la coagulación.</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>APROBADA</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>2026-08-24 14:34:38</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>X027</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BANCO_PREGUNTAS_GENERALES.xlsx
+++ b/BANCO_PREGUNTAS_GENERALES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O203"/>
+  <dimension ref="A1:O204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15251,6 +15251,79 @@
         </is>
       </c>
     </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>PTRS-000003</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Restricciones</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Producto / Alternativas seguras</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Nivel 1</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Producto-Alternativas seguras</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Para el producto FITO MELATONINA, ¿cuál de las siguientes corresponde a una alternativa segura?</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>FITO ESENCIA FLORAL INSOMNIO; medidas de higiene del sueño; valoración médica cuando el insomnio sea persistente.</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>FITO VITAMINA D3; FITO CLORURO DE MAGNESIO (según objetivo)</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>FITO RESVERATROL o antioxidantes alternativos según perfil</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>Recomendar valoración médica antes de aumentar el consumo de proteínas.</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>APROBADA</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>2026-08-24 15:03:39</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>X017</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
